--- a/call-list/私立高校_架電リスト_全体（北海道〜中部）.xlsx
+++ b/call-list/私立高校_架電リスト_全体（北海道〜中部）.xlsx
@@ -12,7 +12,7 @@
     <sheet name="使い方・注意事項" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'架電リスト'!$A$4:$O$709</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'架電リスト'!$A$4:$O$752</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'架電リスト'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -573,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O709"/>
+  <dimension ref="A1:O752"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>私立高等学校 架電リスト（北海道・東北・関東・中部20都道県／705校）</t>
+          <t>私立高等学校 架電リスト（北海道・東北・関東・中部21都道県／748校）</t>
         </is>
       </c>
     </row>
@@ -42227,9 +42227,2546 @@
         </is>
       </c>
     </row>
+    <row r="710">
+      <c r="A710" s="4" t="n">
+        <v>706</v>
+      </c>
+      <c r="B710" s="5" t="inlineStr">
+        <is>
+          <t>静岡県</t>
+        </is>
+      </c>
+      <c r="C710" s="5" t="inlineStr">
+        <is>
+          <t>磐田市</t>
+        </is>
+      </c>
+      <c r="D710" s="5" t="inlineStr">
+        <is>
+          <t>磐田東高等学校</t>
+        </is>
+      </c>
+      <c r="E710" s="6" t="inlineStr">
+        <is>
+          <t>0538-32-6118</t>
+        </is>
+      </c>
+      <c r="F710" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G710" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H710" s="8" t="n"/>
+      <c r="I710" s="9" t="n"/>
+      <c r="J710" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K710" s="8" t="n"/>
+      <c r="L710" s="9" t="n"/>
+      <c r="M710" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認。中高共通</t>
+        </is>
+      </c>
+      <c r="N710" s="11" t="inlineStr">
+        <is>
+          <t>https://www.iwatahigashi-h.ed.jp/ ; https://www.mapion.co.jp/phonebook/M11004/22211/ILSP0000041612_ipclm/</t>
+        </is>
+      </c>
+      <c r="O710" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="4" t="n">
+        <v>707</v>
+      </c>
+      <c r="B711" s="5" t="inlineStr">
+        <is>
+          <t>静岡県</t>
+        </is>
+      </c>
+      <c r="C711" s="5" t="inlineStr">
+        <is>
+          <t>浜松市中央区</t>
+        </is>
+      </c>
+      <c r="D711" s="5" t="inlineStr">
+        <is>
+          <t>オイスカ浜松国際高等学校</t>
+        </is>
+      </c>
+      <c r="E711" s="6" t="inlineStr">
+        <is>
+          <t>053-486-3011</t>
+        </is>
+      </c>
+      <c r="F711" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G711" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H711" s="8" t="n"/>
+      <c r="I711" s="9" t="n"/>
+      <c r="J711" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K711" s="8" t="n"/>
+      <c r="L711" s="9" t="n"/>
+      <c r="M711" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認。所在地は浜松市中央区</t>
+        </is>
+      </c>
+      <c r="N711" s="11" t="inlineStr">
+        <is>
+          <t>https://www.oisca.ed.jp/school/access/ ; https://www.minkou.jp/hischool/school/646/</t>
+        </is>
+      </c>
+      <c r="O711" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="4" t="n">
+        <v>708</v>
+      </c>
+      <c r="B712" s="5" t="inlineStr">
+        <is>
+          <t>静岡県</t>
+        </is>
+      </c>
+      <c r="C712" s="5" t="inlineStr">
+        <is>
+          <t>沼津市</t>
+        </is>
+      </c>
+      <c r="D712" s="5" t="inlineStr">
+        <is>
+          <t>加藤学園暁秀高等学校</t>
+        </is>
+      </c>
+      <c r="E712" s="6" t="inlineStr">
+        <is>
+          <t>055-924-1900</t>
+        </is>
+      </c>
+      <c r="F712" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G712" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H712" s="8" t="n"/>
+      <c r="I712" s="9" t="n"/>
+      <c r="J712" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K712" s="8" t="n"/>
+      <c r="L712" s="9" t="n"/>
+      <c r="M712" s="10" t="inlineStr">
+        <is>
+          <t>中高共通。加藤学園高校とは別の学校</t>
+        </is>
+      </c>
+      <c r="N712" s="11" t="inlineStr">
+        <is>
+          <t>https://www.mapion.co.jp/phonebook/M11004/22203/ILSP0000041290_ipclm/ ; https://school.js88.com/scl_h/22009120</t>
+        </is>
+      </c>
+      <c r="O712" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="4" t="n">
+        <v>709</v>
+      </c>
+      <c r="B713" s="5" t="inlineStr">
+        <is>
+          <t>静岡県</t>
+        </is>
+      </c>
+      <c r="C713" s="5" t="inlineStr">
+        <is>
+          <t>沼津市</t>
+        </is>
+      </c>
+      <c r="D713" s="5" t="inlineStr">
+        <is>
+          <t>加藤学園高等学校</t>
+        </is>
+      </c>
+      <c r="E713" s="6" t="inlineStr">
+        <is>
+          <t>055-921-0347</t>
+        </is>
+      </c>
+      <c r="F713" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G713" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H713" s="8" t="n"/>
+      <c r="I713" s="9" t="n"/>
+      <c r="J713" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K713" s="8" t="n"/>
+      <c r="L713" s="9" t="n"/>
+      <c r="M713" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトに「代表」と記載。加藤学園暁秀とは別の学校</t>
+        </is>
+      </c>
+      <c r="N713" s="11" t="inlineStr">
+        <is>
+          <t>https://www.katogaku.jp/KatohHS/</t>
+        </is>
+      </c>
+      <c r="O713" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="4" t="n">
+        <v>710</v>
+      </c>
+      <c r="B714" s="5" t="inlineStr">
+        <is>
+          <t>静岡県</t>
+        </is>
+      </c>
+      <c r="C714" s="5" t="inlineStr">
+        <is>
+          <t>吉田町</t>
+        </is>
+      </c>
+      <c r="D714" s="5" t="inlineStr">
+        <is>
+          <t>キラリ高等学校</t>
+        </is>
+      </c>
+      <c r="E714" s="6" t="inlineStr">
+        <is>
+          <t>0548-33-4976</t>
+        </is>
+      </c>
+      <c r="F714" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G714" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H714" s="8" t="n"/>
+      <c r="I714" s="9" t="n"/>
+      <c r="J714" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K714" s="8" t="n"/>
+      <c r="L714" s="9" t="n"/>
+      <c r="M714" s="10" t="inlineStr">
+        <is>
+          <t>通信制。吉田本校の番号（公式サイト）</t>
+        </is>
+      </c>
+      <c r="N714" s="11" t="inlineStr">
+        <is>
+          <t>https://www.kirari-highschool.jp/introduction/access/</t>
+        </is>
+      </c>
+      <c r="O714" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="4" t="n">
+        <v>711</v>
+      </c>
+      <c r="B715" s="5" t="inlineStr">
+        <is>
+          <t>静岡県</t>
+        </is>
+      </c>
+      <c r="C715" s="5" t="inlineStr">
+        <is>
+          <t>御殿場市</t>
+        </is>
+      </c>
+      <c r="D715" s="5" t="inlineStr">
+        <is>
+          <t>御殿場西高等学校</t>
+        </is>
+      </c>
+      <c r="E715" s="6" t="inlineStr">
+        <is>
+          <t>0550-89-2466</t>
+        </is>
+      </c>
+      <c r="F715" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G715" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H715" s="8" t="n"/>
+      <c r="I715" s="9" t="n"/>
+      <c r="J715" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K715" s="8" t="n"/>
+      <c r="L715" s="9" t="n"/>
+      <c r="M715" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認</t>
+        </is>
+      </c>
+      <c r="N715" s="11" t="inlineStr">
+        <is>
+          <t>https://gotembanishi-h.ed.jp/access/</t>
+        </is>
+      </c>
+      <c r="O715" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="4" t="n">
+        <v>712</v>
+      </c>
+      <c r="B716" s="5" t="inlineStr">
+        <is>
+          <t>静岡県</t>
+        </is>
+      </c>
+      <c r="C716" s="5" t="inlineStr">
+        <is>
+          <t>静岡市葵区</t>
+        </is>
+      </c>
+      <c r="D716" s="5" t="inlineStr">
+        <is>
+          <t>静岡英和女学院高等学校</t>
+        </is>
+      </c>
+      <c r="E716" s="6" t="inlineStr">
+        <is>
+          <t>054-254-7401</t>
+        </is>
+      </c>
+      <c r="F716" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G716" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H716" s="8" t="n"/>
+      <c r="I716" s="9" t="n"/>
+      <c r="J716" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K716" s="8" t="n"/>
+      <c r="L716" s="9" t="n"/>
+      <c r="M716" s="10" t="inlineStr">
+        <is>
+          <t>中高共通。2つのサイトで一致</t>
+        </is>
+      </c>
+      <c r="N716" s="11" t="inlineStr">
+        <is>
+          <t>https://www.mapion.co.jp/phonebook/M11004/22101/ILSP0000040742_ipclm/ ; https://shizu-hsmap.com/3460/</t>
+        </is>
+      </c>
+      <c r="O716" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" s="4" t="n">
+        <v>713</v>
+      </c>
+      <c r="B717" s="5" t="inlineStr">
+        <is>
+          <t>静岡県</t>
+        </is>
+      </c>
+      <c r="C717" s="5" t="inlineStr">
+        <is>
+          <t>静岡市葵区</t>
+        </is>
+      </c>
+      <c r="D717" s="5" t="inlineStr">
+        <is>
+          <t>静岡学園高等学校</t>
+        </is>
+      </c>
+      <c r="E717" s="6" t="inlineStr">
+        <is>
+          <t>054-200-0191</t>
+        </is>
+      </c>
+      <c r="F717" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G717" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H717" s="8" t="n"/>
+      <c r="I717" s="9" t="n"/>
+      <c r="J717" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K717" s="8" t="n"/>
+      <c r="L717" s="9" t="n"/>
+      <c r="M717" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認。中高共通</t>
+        </is>
+      </c>
+      <c r="N717" s="11" t="inlineStr">
+        <is>
+          <t>https://www.shizugaku.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O717" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" s="4" t="n">
+        <v>714</v>
+      </c>
+      <c r="B718" s="5" t="inlineStr">
+        <is>
+          <t>静岡県</t>
+        </is>
+      </c>
+      <c r="C718" s="5" t="inlineStr">
+        <is>
+          <t>静岡市葵区</t>
+        </is>
+      </c>
+      <c r="D718" s="5" t="inlineStr">
+        <is>
+          <t>静岡北高等学校</t>
+        </is>
+      </c>
+      <c r="E718" s="6" t="inlineStr">
+        <is>
+          <t>054-261-5801</t>
+        </is>
+      </c>
+      <c r="F718" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G718" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H718" s="8" t="n"/>
+      <c r="I718" s="9" t="n"/>
+      <c r="J718" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K718" s="8" t="n"/>
+      <c r="L718" s="9" t="n"/>
+      <c r="M718" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトに「代表」と記載。中学校は054-267-6151</t>
+        </is>
+      </c>
+      <c r="N718" s="11" t="inlineStr">
+        <is>
+          <t>https://shizukita.jp/contact/</t>
+        </is>
+      </c>
+      <c r="O718" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" s="4" t="n">
+        <v>715</v>
+      </c>
+      <c r="B719" s="5" t="inlineStr">
+        <is>
+          <t>静岡県</t>
+        </is>
+      </c>
+      <c r="C719" s="5" t="inlineStr">
+        <is>
+          <t>浜松市中央区</t>
+        </is>
+      </c>
+      <c r="D719" s="5" t="inlineStr">
+        <is>
+          <t>静岡県西遠女子学園高等学校</t>
+        </is>
+      </c>
+      <c r="E719" s="6" t="inlineStr">
+        <is>
+          <t>053-461-0374</t>
+        </is>
+      </c>
+      <c r="F719" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G719" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H719" s="8" t="n"/>
+      <c r="I719" s="9" t="n"/>
+      <c r="J719" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K719" s="8" t="n"/>
+      <c r="L719" s="9" t="n"/>
+      <c r="M719" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認。中高共通。所在地は浜松市中央区</t>
+        </is>
+      </c>
+      <c r="N719" s="11" t="inlineStr">
+        <is>
+          <t>https://www.seien.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O719" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" s="4" t="n">
+        <v>716</v>
+      </c>
+      <c r="B720" s="5" t="inlineStr">
+        <is>
+          <t>静岡県</t>
+        </is>
+      </c>
+      <c r="C720" s="5" t="inlineStr">
+        <is>
+          <t>富士市</t>
+        </is>
+      </c>
+      <c r="D720" s="5" t="inlineStr">
+        <is>
+          <t>静岡県富士見高等学校</t>
+        </is>
+      </c>
+      <c r="E720" s="6" t="inlineStr">
+        <is>
+          <t>0545-61-0250</t>
+        </is>
+      </c>
+      <c r="F720" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G720" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H720" s="8" t="n"/>
+      <c r="I720" s="9" t="n"/>
+      <c r="J720" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K720" s="8" t="n"/>
+      <c r="L720" s="9" t="n"/>
+      <c r="M720" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認。中高共通</t>
+        </is>
+      </c>
+      <c r="N720" s="11" t="inlineStr">
+        <is>
+          <t>https://fujimi.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O720" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" s="4" t="n">
+        <v>717</v>
+      </c>
+      <c r="B721" s="5" t="inlineStr">
+        <is>
+          <t>静岡県</t>
+        </is>
+      </c>
+      <c r="C721" s="5" t="inlineStr">
+        <is>
+          <t>静岡市清水区</t>
+        </is>
+      </c>
+      <c r="D721" s="5" t="inlineStr">
+        <is>
+          <t>静岡サレジオ高等学校</t>
+        </is>
+      </c>
+      <c r="E721" s="6" t="inlineStr">
+        <is>
+          <t>054-345-2296</t>
+        </is>
+      </c>
+      <c r="F721" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G721" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H721" s="8" t="n"/>
+      <c r="I721" s="9" t="n"/>
+      <c r="J721" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K721" s="8" t="n"/>
+      <c r="L721" s="9" t="n"/>
+      <c r="M721" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認</t>
+        </is>
+      </c>
+      <c r="N721" s="11" t="inlineStr">
+        <is>
+          <t>https://ssalesio.ac.jp/high/contact/</t>
+        </is>
+      </c>
+      <c r="O721" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" s="4" t="n">
+        <v>718</v>
+      </c>
+      <c r="B722" s="5" t="inlineStr">
+        <is>
+          <t>静岡県</t>
+        </is>
+      </c>
+      <c r="C722" s="5" t="inlineStr">
+        <is>
+          <t>静岡市駿河区</t>
+        </is>
+      </c>
+      <c r="D722" s="5" t="inlineStr">
+        <is>
+          <t>静岡女子高等学校</t>
+        </is>
+      </c>
+      <c r="E722" s="6" t="inlineStr">
+        <is>
+          <t>054-285-2274</t>
+        </is>
+      </c>
+      <c r="F722" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G722" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H722" s="8" t="n"/>
+      <c r="I722" s="9" t="n"/>
+      <c r="J722" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K722" s="8" t="n"/>
+      <c r="L722" s="9" t="n"/>
+      <c r="M722" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認</t>
+        </is>
+      </c>
+      <c r="N722" s="11" t="inlineStr">
+        <is>
+          <t>https://shizuoka-joshi.ac.jp/</t>
+        </is>
+      </c>
+      <c r="O722" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" s="4" t="n">
+        <v>719</v>
+      </c>
+      <c r="B723" s="5" t="inlineStr">
+        <is>
+          <t>静岡県</t>
+        </is>
+      </c>
+      <c r="C723" s="5" t="inlineStr">
+        <is>
+          <t>静岡市駿河区</t>
+        </is>
+      </c>
+      <c r="D723" s="5" t="inlineStr">
+        <is>
+          <t>静岡聖光学院高等学校</t>
+        </is>
+      </c>
+      <c r="E723" s="6" t="inlineStr">
+        <is>
+          <t>054-285-9136</t>
+        </is>
+      </c>
+      <c r="F723" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G723" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H723" s="8" t="n"/>
+      <c r="I723" s="9" t="n"/>
+      <c r="J723" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K723" s="8" t="n"/>
+      <c r="L723" s="9" t="n"/>
+      <c r="M723" s="10" t="inlineStr">
+        <is>
+          <t>中高共通。高校募集なし（完全中高一貫）。公式未確認</t>
+        </is>
+      </c>
+      <c r="N723" s="11" t="inlineStr">
+        <is>
+          <t>https://www.mapion.co.jp/phonebook/M11004/22102/ILSP0000041139_ipclm/ ; https://itp.ne.jp/info/229451737200000899/</t>
+        </is>
+      </c>
+      <c r="O723" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" s="4" t="n">
+        <v>720</v>
+      </c>
+      <c r="B724" s="5" t="inlineStr">
+        <is>
+          <t>静岡県</t>
+        </is>
+      </c>
+      <c r="C724" s="5" t="inlineStr">
+        <is>
+          <t>静岡市葵区</t>
+        </is>
+      </c>
+      <c r="D724" s="5" t="inlineStr">
+        <is>
+          <t>静岡大成高等学校</t>
+        </is>
+      </c>
+      <c r="E724" s="6" t="inlineStr">
+        <is>
+          <t>054-254-7334</t>
+        </is>
+      </c>
+      <c r="F724" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G724" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H724" s="8" t="n"/>
+      <c r="I724" s="9" t="n"/>
+      <c r="J724" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K724" s="8" t="n"/>
+      <c r="L724" s="9" t="n"/>
+      <c r="M724" s="10" t="inlineStr">
+        <is>
+          <t>複数サイトで一致、公式未確認</t>
+        </is>
+      </c>
+      <c r="N724" s="11" t="inlineStr">
+        <is>
+          <t>https://www.mapion.co.jp/phonebook/M11004/22101/ILSP0000040794_ipclm/</t>
+        </is>
+      </c>
+      <c r="O724" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" s="4" t="n">
+        <v>721</v>
+      </c>
+      <c r="B725" s="5" t="inlineStr">
+        <is>
+          <t>静岡県</t>
+        </is>
+      </c>
+      <c r="C725" s="5" t="inlineStr">
+        <is>
+          <t>静岡市葵区</t>
+        </is>
+      </c>
+      <c r="D725" s="5" t="inlineStr">
+        <is>
+          <t>静岡雙葉高等学校</t>
+        </is>
+      </c>
+      <c r="E725" s="6" t="inlineStr">
+        <is>
+          <t>054-255-0305</t>
+        </is>
+      </c>
+      <c r="F725" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G725" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H725" s="8" t="n"/>
+      <c r="I725" s="9" t="n"/>
+      <c r="J725" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K725" s="8" t="n"/>
+      <c r="L725" s="9" t="n"/>
+      <c r="M725" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認。中高共通</t>
+        </is>
+      </c>
+      <c r="N725" s="11" t="inlineStr">
+        <is>
+          <t>https://shizuoka-futaba.ac.jp/graduate/certificate/ ; https://www.mapion.co.jp/phonebook/M11004/22101/ILSP0000041364_ipclm/</t>
+        </is>
+      </c>
+      <c r="O725" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" s="4" t="n">
+        <v>722</v>
+      </c>
+      <c r="B726" s="5" t="inlineStr">
+        <is>
+          <t>静岡県</t>
+        </is>
+      </c>
+      <c r="C726" s="5" t="inlineStr">
+        <is>
+          <t>島田市</t>
+        </is>
+      </c>
+      <c r="D726" s="5" t="inlineStr">
+        <is>
+          <t>島田樟誠高等学校</t>
+        </is>
+      </c>
+      <c r="E726" s="6" t="inlineStr">
+        <is>
+          <t>0547-37-3116</t>
+        </is>
+      </c>
+      <c r="F726" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G726" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H726" s="8" t="n"/>
+      <c r="I726" s="9" t="n"/>
+      <c r="J726" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K726" s="8" t="n"/>
+      <c r="L726" s="9" t="n"/>
+      <c r="M726" s="10" t="inlineStr">
+        <is>
+          <t>複数サイトで一致、公式未確認</t>
+        </is>
+      </c>
+      <c r="N726" s="11" t="inlineStr">
+        <is>
+          <t>https://www.mapion.co.jp/phonebook/M11004/22209/ILSP0000041690_ipclm/ ; https://www.minkou.jp/hischool/school/2271/</t>
+        </is>
+      </c>
+      <c r="O726" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" s="4" t="n">
+        <v>723</v>
+      </c>
+      <c r="B727" s="5" t="inlineStr">
+        <is>
+          <t>静岡県</t>
+        </is>
+      </c>
+      <c r="C727" s="5" t="inlineStr">
+        <is>
+          <t>静岡市清水区</t>
+        </is>
+      </c>
+      <c r="D727" s="5" t="inlineStr">
+        <is>
+          <t>清水国際高等学校</t>
+        </is>
+      </c>
+      <c r="E727" s="6" t="inlineStr">
+        <is>
+          <t>054-366-4155</t>
+        </is>
+      </c>
+      <c r="F727" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G727" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H727" s="8" t="n"/>
+      <c r="I727" s="9" t="n"/>
+      <c r="J727" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K727" s="8" t="n"/>
+      <c r="L727" s="9" t="n"/>
+      <c r="M727" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認</t>
+        </is>
+      </c>
+      <c r="N727" s="11" t="inlineStr">
+        <is>
+          <t>https://www.shimizu-kokusai.ac.jp/</t>
+        </is>
+      </c>
+      <c r="O727" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" s="4" t="n">
+        <v>724</v>
+      </c>
+      <c r="B728" s="5" t="inlineStr">
+        <is>
+          <t>静岡県</t>
+        </is>
+      </c>
+      <c r="C728" s="5" t="inlineStr">
+        <is>
+          <t>静岡市駿河区</t>
+        </is>
+      </c>
+      <c r="D728" s="5" t="inlineStr">
+        <is>
+          <t>城南静岡高等学校</t>
+        </is>
+      </c>
+      <c r="E728" s="6" t="inlineStr">
+        <is>
+          <t>054-285-6156</t>
+        </is>
+      </c>
+      <c r="F728" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G728" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H728" s="8" t="n"/>
+      <c r="I728" s="9" t="n"/>
+      <c r="J728" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K728" s="8" t="n"/>
+      <c r="L728" s="9" t="n"/>
+      <c r="M728" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認。中高共通</t>
+        </is>
+      </c>
+      <c r="N728" s="11" t="inlineStr">
+        <is>
+          <t>https://www.johnan.ac.jp/</t>
+        </is>
+      </c>
+      <c r="O728" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" s="4" t="n">
+        <v>725</v>
+      </c>
+      <c r="B729" s="5" t="inlineStr">
+        <is>
+          <t>静岡県</t>
+        </is>
+      </c>
+      <c r="C729" s="5" t="inlineStr">
+        <is>
+          <t>沼津市</t>
+        </is>
+      </c>
+      <c r="D729" s="5" t="inlineStr">
+        <is>
+          <t>誠恵高等学校</t>
+        </is>
+      </c>
+      <c r="E729" s="6" t="inlineStr">
+        <is>
+          <t>055-921-5088</t>
+        </is>
+      </c>
+      <c r="F729" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G729" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H729" s="8" t="n"/>
+      <c r="I729" s="9" t="n"/>
+      <c r="J729" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K729" s="8" t="n"/>
+      <c r="L729" s="9" t="n"/>
+      <c r="M729" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトに「代表」と記載</t>
+        </is>
+      </c>
+      <c r="N729" s="11" t="inlineStr">
+        <is>
+          <t>http://www.seikei-on.ac.jp/contact/</t>
+        </is>
+      </c>
+      <c r="O729" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" s="4" t="n">
+        <v>726</v>
+      </c>
+      <c r="B730" s="5" t="inlineStr">
+        <is>
+          <t>静岡県</t>
+        </is>
+      </c>
+      <c r="C730" s="5" t="inlineStr">
+        <is>
+          <t>藤枝市</t>
+        </is>
+      </c>
+      <c r="D730" s="5" t="inlineStr">
+        <is>
+          <t>静清高等学校</t>
+        </is>
+      </c>
+      <c r="E730" s="6" t="inlineStr">
+        <is>
+          <t>054-641-6693</t>
+        </is>
+      </c>
+      <c r="F730" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G730" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H730" s="8" t="n"/>
+      <c r="I730" s="9" t="n"/>
+      <c r="J730" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K730" s="8" t="n"/>
+      <c r="L730" s="9" t="n"/>
+      <c r="M730" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認。通信制課程も同じ番号</t>
+        </is>
+      </c>
+      <c r="N730" s="11" t="inlineStr">
+        <is>
+          <t>https://seisei.ed.jp/access/</t>
+        </is>
+      </c>
+      <c r="O730" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" s="4" t="n">
+        <v>727</v>
+      </c>
+      <c r="B731" s="5" t="inlineStr">
+        <is>
+          <t>静岡県</t>
+        </is>
+      </c>
+      <c r="C731" s="5" t="inlineStr">
+        <is>
+          <t>富士宮市</t>
+        </is>
+      </c>
+      <c r="D731" s="5" t="inlineStr">
+        <is>
+          <t>星陵高等学校</t>
+        </is>
+      </c>
+      <c r="E731" s="6" t="inlineStr">
+        <is>
+          <t>0544-24-4811</t>
+        </is>
+      </c>
+      <c r="F731" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G731" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H731" s="8" t="n"/>
+      <c r="I731" s="9" t="n"/>
+      <c r="J731" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K731" s="8" t="n"/>
+      <c r="L731" s="9" t="n"/>
+      <c r="M731" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認（静岡理工科大学星陵中学校・高等学校）</t>
+        </is>
+      </c>
+      <c r="N731" s="11" t="inlineStr">
+        <is>
+          <t>https://starhill.ed.jp/hs/</t>
+        </is>
+      </c>
+      <c r="O731" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" s="4" t="n">
+        <v>728</v>
+      </c>
+      <c r="B732" s="5" t="inlineStr">
+        <is>
+          <t>静岡県</t>
+        </is>
+      </c>
+      <c r="C732" s="5" t="inlineStr">
+        <is>
+          <t>浜松市中央区</t>
+        </is>
+      </c>
+      <c r="D732" s="5" t="inlineStr">
+        <is>
+          <t>聖隷クリストファー高等学校</t>
+        </is>
+      </c>
+      <c r="E732" s="6" t="inlineStr">
+        <is>
+          <t>053-436-5313</t>
+        </is>
+      </c>
+      <c r="F732" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G732" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H732" s="8" t="n"/>
+      <c r="I732" s="9" t="n"/>
+      <c r="J732" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K732" s="8" t="n"/>
+      <c r="L732" s="9" t="n"/>
+      <c r="M732" s="10" t="inlineStr">
+        <is>
+          <t>複数サイトで一致、公式未確認。所在地は浜松市中央区</t>
+        </is>
+      </c>
+      <c r="N732" s="11" t="inlineStr">
+        <is>
+          <t>https://www.mapion.co.jp/phonebook/M11004/22138/ILSP0000041195_ipclm/ ; https://school.js88.com/scl_h/22009420</t>
+        </is>
+      </c>
+      <c r="O732" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" s="4" t="n">
+        <v>729</v>
+      </c>
+      <c r="B733" s="5" t="inlineStr">
+        <is>
+          <t>静岡県</t>
+        </is>
+      </c>
+      <c r="C733" s="5" t="inlineStr">
+        <is>
+          <t>長泉町</t>
+        </is>
+      </c>
+      <c r="D733" s="5" t="inlineStr">
+        <is>
+          <t>知徳高等学校</t>
+        </is>
+      </c>
+      <c r="E733" s="6" t="inlineStr">
+        <is>
+          <t>055-975-0080</t>
+        </is>
+      </c>
+      <c r="F733" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G733" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H733" s="8" t="n"/>
+      <c r="I733" s="9" t="n"/>
+      <c r="J733" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K733" s="8" t="n"/>
+      <c r="L733" s="9" t="n"/>
+      <c r="M733" s="10" t="inlineStr">
+        <is>
+          <t>複数サイトで一致。055-976-0735はFAXなので注意</t>
+        </is>
+      </c>
+      <c r="N733" s="11" t="inlineStr">
+        <is>
+          <t>https://www.mapion.co.jp/phonebook/M11004/22342/ILSP0000041799_ipclm/ ; https://itp.ne.jp/info/225247068200000899/</t>
+        </is>
+      </c>
+      <c r="O733" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" s="4" t="n">
+        <v>730</v>
+      </c>
+      <c r="B734" s="5" t="inlineStr">
+        <is>
+          <t>静岡県</t>
+        </is>
+      </c>
+      <c r="C734" s="5" t="inlineStr">
+        <is>
+          <t>静岡市清水区</t>
+        </is>
+      </c>
+      <c r="D734" s="5" t="inlineStr">
+        <is>
+          <t>東海大学付属静岡翔洋高等学校</t>
+        </is>
+      </c>
+      <c r="E734" s="6" t="inlineStr">
+        <is>
+          <t>054-334-0726</t>
+        </is>
+      </c>
+      <c r="F734" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G734" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H734" s="8" t="n"/>
+      <c r="I734" s="9" t="n"/>
+      <c r="J734" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K734" s="8" t="n"/>
+      <c r="L734" s="9" t="n"/>
+      <c r="M734" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認。中等部は054-334-1851</t>
+        </is>
+      </c>
+      <c r="N734" s="11" t="inlineStr">
+        <is>
+          <t>https://www.shoyo.tokai.ed.jp/contact/</t>
+        </is>
+      </c>
+      <c r="O734" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" s="4" t="n">
+        <v>731</v>
+      </c>
+      <c r="B735" s="5" t="inlineStr">
+        <is>
+          <t>静岡県</t>
+        </is>
+      </c>
+      <c r="C735" s="5" t="inlineStr">
+        <is>
+          <t>沼津市</t>
+        </is>
+      </c>
+      <c r="D735" s="5" t="inlineStr">
+        <is>
+          <t>桐陽高等学校</t>
+        </is>
+      </c>
+      <c r="E735" s="6" t="inlineStr">
+        <is>
+          <t>055-921-0350</t>
+        </is>
+      </c>
+      <c r="F735" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G735" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H735" s="8" t="n"/>
+      <c r="I735" s="9" t="n"/>
+      <c r="J735" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K735" s="8" t="n"/>
+      <c r="L735" s="9" t="n"/>
+      <c r="M735" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトでは募集広報部の番号。055-921-0096を載せるサイトもあり（旧番号の可能性）</t>
+        </is>
+      </c>
+      <c r="N735" s="11" t="inlineStr">
+        <is>
+          <t>https://toyo-numazu.ac.jp/contact/ ; https://www.mapion.co.jp/phonebook/M11004/22203/ILSP0000041817_ipclm/</t>
+        </is>
+      </c>
+      <c r="O735" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" s="4" t="n">
+        <v>732</v>
+      </c>
+      <c r="B736" s="5" t="inlineStr">
+        <is>
+          <t>静岡県</t>
+        </is>
+      </c>
+      <c r="C736" s="5" t="inlineStr">
+        <is>
+          <t>菊川市</t>
+        </is>
+      </c>
+      <c r="D736" s="5" t="inlineStr">
+        <is>
+          <t>常葉大学附属菊川高等学校</t>
+        </is>
+      </c>
+      <c r="E736" s="6" t="inlineStr">
+        <is>
+          <t>0537-35-3171</t>
+        </is>
+      </c>
+      <c r="F736" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G736" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H736" s="8" t="n"/>
+      <c r="I736" s="9" t="n"/>
+      <c r="J736" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K736" s="8" t="n"/>
+      <c r="L736" s="9" t="n"/>
+      <c r="M736" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認。中高共通</t>
+        </is>
+      </c>
+      <c r="N736" s="11" t="inlineStr">
+        <is>
+          <t>https://tokoha.net/kikugawa/guide/access/</t>
+        </is>
+      </c>
+      <c r="O736" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" s="4" t="n">
+        <v>733</v>
+      </c>
+      <c r="B737" s="5" t="inlineStr">
+        <is>
+          <t>静岡県</t>
+        </is>
+      </c>
+      <c r="C737" s="5" t="inlineStr">
+        <is>
+          <t>静岡市葵区</t>
+        </is>
+      </c>
+      <c r="D737" s="5" t="inlineStr">
+        <is>
+          <t>常葉大学附属橘高等学校</t>
+        </is>
+      </c>
+      <c r="E737" s="6" t="inlineStr">
+        <is>
+          <t>054-261-2256</t>
+        </is>
+      </c>
+      <c r="F737" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G737" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H737" s="8" t="n"/>
+      <c r="I737" s="9" t="n"/>
+      <c r="J737" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K737" s="8" t="n"/>
+      <c r="L737" s="9" t="n"/>
+      <c r="M737" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認。中高共通</t>
+        </is>
+      </c>
+      <c r="N737" s="11" t="inlineStr">
+        <is>
+          <t>https://www.tokoha.ac.jp/tachibana-jh/</t>
+        </is>
+      </c>
+      <c r="O737" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" s="4" t="n">
+        <v>734</v>
+      </c>
+      <c r="B738" s="5" t="inlineStr">
+        <is>
+          <t>静岡県</t>
+        </is>
+      </c>
+      <c r="C738" s="5" t="inlineStr">
+        <is>
+          <t>静岡市葵区</t>
+        </is>
+      </c>
+      <c r="D738" s="5" t="inlineStr">
+        <is>
+          <t>常葉大学附属常葉高等学校</t>
+        </is>
+      </c>
+      <c r="E738" s="6" t="inlineStr">
+        <is>
+          <t>054-245-5401</t>
+        </is>
+      </c>
+      <c r="F738" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G738" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H738" s="8" t="n"/>
+      <c r="I738" s="9" t="n"/>
+      <c r="J738" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K738" s="8" t="n"/>
+      <c r="L738" s="9" t="n"/>
+      <c r="M738" s="10" t="inlineStr">
+        <is>
+          <t>中高共通の代表</t>
+        </is>
+      </c>
+      <c r="N738" s="11" t="inlineStr">
+        <is>
+          <t>https://www.tokoha-u.ac.jp/university/links/ ; https://www.mapion.co.jp/phonebook/M11004/22101/ILSP0000041765_ipclm/</t>
+        </is>
+      </c>
+      <c r="O738" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" s="4" t="n">
+        <v>735</v>
+      </c>
+      <c r="B739" s="5" t="inlineStr">
+        <is>
+          <t>静岡県</t>
+        </is>
+      </c>
+      <c r="C739" s="5" t="inlineStr">
+        <is>
+          <t>三島市</t>
+        </is>
+      </c>
+      <c r="D739" s="5" t="inlineStr">
+        <is>
+          <t>日本大学三島高等学校</t>
+        </is>
+      </c>
+      <c r="E739" s="6" t="inlineStr">
+        <is>
+          <t>055-988-3500</t>
+        </is>
+      </c>
+      <c r="F739" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G739" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H739" s="8" t="n"/>
+      <c r="I739" s="9" t="n"/>
+      <c r="J739" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K739" s="8" t="n"/>
+      <c r="L739" s="9" t="n"/>
+      <c r="M739" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認。中高共通</t>
+        </is>
+      </c>
+      <c r="N739" s="11" t="inlineStr">
+        <is>
+          <t>https://www.mishima.hs.nihon-u.ac.jp/</t>
+        </is>
+      </c>
+      <c r="O739" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" s="4" t="n">
+        <v>736</v>
+      </c>
+      <c r="B740" s="5" t="inlineStr">
+        <is>
+          <t>静岡県</t>
+        </is>
+      </c>
+      <c r="C740" s="5" t="inlineStr">
+        <is>
+          <t>沼津市</t>
+        </is>
+      </c>
+      <c r="D740" s="5" t="inlineStr">
+        <is>
+          <t>沼津中央高等学校</t>
+        </is>
+      </c>
+      <c r="E740" s="6" t="inlineStr">
+        <is>
+          <t>055-921-0346</t>
+        </is>
+      </c>
+      <c r="F740" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G740" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H740" s="8" t="n"/>
+      <c r="I740" s="9" t="n"/>
+      <c r="J740" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K740" s="8" t="n"/>
+      <c r="L740" s="9" t="n"/>
+      <c r="M740" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認</t>
+        </is>
+      </c>
+      <c r="N740" s="11" t="inlineStr">
+        <is>
+          <t>https://www.n-chuo.ac.jp/contact ; https://www.mapion.co.jp/phonebook/M11004/22203/ILSP0000041058_ipclm/</t>
+        </is>
+      </c>
+      <c r="O740" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" s="4" t="n">
+        <v>737</v>
+      </c>
+      <c r="B741" s="5" t="inlineStr">
+        <is>
+          <t>静岡県</t>
+        </is>
+      </c>
+      <c r="C741" s="5" t="inlineStr">
+        <is>
+          <t>浜松市中央区</t>
+        </is>
+      </c>
+      <c r="D741" s="5" t="inlineStr">
+        <is>
+          <t>浜松開誠館高等学校</t>
+        </is>
+      </c>
+      <c r="E741" s="6" t="inlineStr">
+        <is>
+          <t>053-456-7111</t>
+        </is>
+      </c>
+      <c r="F741" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G741" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H741" s="8" t="n"/>
+      <c r="I741" s="9" t="n"/>
+      <c r="J741" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K741" s="8" t="n"/>
+      <c r="L741" s="9" t="n"/>
+      <c r="M741" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認。中高共通</t>
+        </is>
+      </c>
+      <c r="N741" s="11" t="inlineStr">
+        <is>
+          <t>https://www.kaiseikan.ed.jp/top-page/school-overview/</t>
+        </is>
+      </c>
+      <c r="O741" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" s="4" t="n">
+        <v>738</v>
+      </c>
+      <c r="B742" s="5" t="inlineStr">
+        <is>
+          <t>静岡県</t>
+        </is>
+      </c>
+      <c r="C742" s="5" t="inlineStr">
+        <is>
+          <t>浜松市中央区</t>
+        </is>
+      </c>
+      <c r="D742" s="5" t="inlineStr">
+        <is>
+          <t>浜松学院高等学校</t>
+        </is>
+      </c>
+      <c r="E742" s="6" t="inlineStr">
+        <is>
+          <t>053-471-4136</t>
+        </is>
+      </c>
+      <c r="F742" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G742" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H742" s="8" t="n"/>
+      <c r="I742" s="9" t="n"/>
+      <c r="J742" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K742" s="8" t="n"/>
+      <c r="L742" s="9" t="n"/>
+      <c r="M742" s="10" t="inlineStr">
+        <is>
+          <t>【校名変更】2025年4月に「浜松学院興誠高等学校」へ改称。法人本部と同じ番号</t>
+        </is>
+      </c>
+      <c r="N742" s="11" t="inlineStr">
+        <is>
+          <t>https://www.hamagaku.ac.jp/gakuin/schoolprospectus/history/ ; https://school.js88.com/scl_h/22009350</t>
+        </is>
+      </c>
+      <c r="O742" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" s="4" t="n">
+        <v>739</v>
+      </c>
+      <c r="B743" s="5" t="inlineStr">
+        <is>
+          <t>静岡県</t>
+        </is>
+      </c>
+      <c r="C743" s="5" t="inlineStr">
+        <is>
+          <t>浜松市中央区</t>
+        </is>
+      </c>
+      <c r="D743" s="5" t="inlineStr">
+        <is>
+          <t>浜松学芸高等学校</t>
+        </is>
+      </c>
+      <c r="E743" s="6" t="inlineStr">
+        <is>
+          <t>053-471-5336</t>
+        </is>
+      </c>
+      <c r="F743" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G743" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H743" s="8" t="n"/>
+      <c r="I743" s="9" t="n"/>
+      <c r="J743" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K743" s="8" t="n"/>
+      <c r="L743" s="9" t="n"/>
+      <c r="M743" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認</t>
+        </is>
+      </c>
+      <c r="N743" s="11" t="inlineStr">
+        <is>
+          <t>https://www.gakugei.ed.jp/high/</t>
+        </is>
+      </c>
+      <c r="O743" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" s="4" t="n">
+        <v>740</v>
+      </c>
+      <c r="B744" s="5" t="inlineStr">
+        <is>
+          <t>静岡県</t>
+        </is>
+      </c>
+      <c r="C744" s="5" t="inlineStr">
+        <is>
+          <t>浜松市中央区</t>
+        </is>
+      </c>
+      <c r="D744" s="5" t="inlineStr">
+        <is>
+          <t>浜松啓陽高等学校</t>
+        </is>
+      </c>
+      <c r="E744" s="6" t="inlineStr">
+        <is>
+          <t>053-420-0431</t>
+        </is>
+      </c>
+      <c r="F744" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G744" s="5" t="inlineStr">
+        <is>
+          <t>専門学科</t>
+        </is>
+      </c>
+      <c r="H744" s="8" t="n"/>
+      <c r="I744" s="9" t="n"/>
+      <c r="J744" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K744" s="8" t="n"/>
+      <c r="L744" s="9" t="n"/>
+      <c r="M744" s="10" t="inlineStr">
+        <is>
+          <t>通信制。公式サイトで確認</t>
+        </is>
+      </c>
+      <c r="N744" s="11" t="inlineStr">
+        <is>
+          <t>https://keiyo.ed.jp/ ; https://school.js88.com/scl_h/34029510?page=6</t>
+        </is>
+      </c>
+      <c r="O744" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" s="4" t="n">
+        <v>741</v>
+      </c>
+      <c r="B745" s="5" t="inlineStr">
+        <is>
+          <t>静岡県</t>
+        </is>
+      </c>
+      <c r="C745" s="5" t="inlineStr">
+        <is>
+          <t>浜松市中央区</t>
+        </is>
+      </c>
+      <c r="D745" s="5" t="inlineStr">
+        <is>
+          <t>浜松修学舎高等学校</t>
+        </is>
+      </c>
+      <c r="E745" s="6" t="inlineStr">
+        <is>
+          <t>053-461-7356</t>
+        </is>
+      </c>
+      <c r="F745" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G745" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H745" s="8" t="n"/>
+      <c r="I745" s="9" t="n"/>
+      <c r="J745" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K745" s="8" t="n"/>
+      <c r="L745" s="9" t="n"/>
+      <c r="M745" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認</t>
+        </is>
+      </c>
+      <c r="N745" s="11" t="inlineStr">
+        <is>
+          <t>https://www.shugakusha.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O745" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" s="4" t="n">
+        <v>742</v>
+      </c>
+      <c r="B746" s="5" t="inlineStr">
+        <is>
+          <t>静岡県</t>
+        </is>
+      </c>
+      <c r="C746" s="5" t="inlineStr">
+        <is>
+          <t>浜松市中央区</t>
+        </is>
+      </c>
+      <c r="D746" s="5" t="inlineStr">
+        <is>
+          <t>浜松聖星高等学校</t>
+        </is>
+      </c>
+      <c r="E746" s="6" t="inlineStr">
+        <is>
+          <t>053-454-5376</t>
+        </is>
+      </c>
+      <c r="F746" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G746" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H746" s="8" t="n"/>
+      <c r="I746" s="9" t="n"/>
+      <c r="J746" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K746" s="8" t="n"/>
+      <c r="L746" s="9" t="n"/>
+      <c r="M746" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認</t>
+        </is>
+      </c>
+      <c r="N746" s="11" t="inlineStr">
+        <is>
+          <t>https://hamamatsu-seisei.jp/about/school_outline.html</t>
+        </is>
+      </c>
+      <c r="O746" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" s="4" t="n">
+        <v>743</v>
+      </c>
+      <c r="B747" s="5" t="inlineStr">
+        <is>
+          <t>静岡県</t>
+        </is>
+      </c>
+      <c r="C747" s="5" t="inlineStr">
+        <is>
+          <t>浜松市中央区</t>
+        </is>
+      </c>
+      <c r="D747" s="5" t="inlineStr">
+        <is>
+          <t>浜松日体高等学校</t>
+        </is>
+      </c>
+      <c r="E747" s="6" t="inlineStr">
+        <is>
+          <t>053-434-0632</t>
+        </is>
+      </c>
+      <c r="F747" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G747" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H747" s="8" t="n"/>
+      <c r="I747" s="9" t="n"/>
+      <c r="J747" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K747" s="8" t="n"/>
+      <c r="L747" s="9" t="n"/>
+      <c r="M747" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認</t>
+        </is>
+      </c>
+      <c r="N747" s="11" t="inlineStr">
+        <is>
+          <t>https://www.h-nittai.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O747" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" s="4" t="n">
+        <v>744</v>
+      </c>
+      <c r="B748" s="5" t="inlineStr">
+        <is>
+          <t>静岡県</t>
+        </is>
+      </c>
+      <c r="C748" s="5" t="inlineStr">
+        <is>
+          <t>沼津市</t>
+        </is>
+      </c>
+      <c r="D748" s="5" t="inlineStr">
+        <is>
+          <t>飛龍高等学校</t>
+        </is>
+      </c>
+      <c r="E748" s="6" t="inlineStr">
+        <is>
+          <t>055-921-7942</t>
+        </is>
+      </c>
+      <c r="F748" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G748" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H748" s="8" t="n"/>
+      <c r="I748" s="9" t="n"/>
+      <c r="J748" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K748" s="8" t="n"/>
+      <c r="L748" s="9" t="n"/>
+      <c r="M748" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認。055-921-0348を載せるサイトは旧番号の可能性</t>
+        </is>
+      </c>
+      <c r="N748" s="11" t="inlineStr">
+        <is>
+          <t>https://hiryu.ed.jp/about-us/access/</t>
+        </is>
+      </c>
+      <c r="O748" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" s="4" t="n">
+        <v>745</v>
+      </c>
+      <c r="B749" s="5" t="inlineStr">
+        <is>
+          <t>静岡県</t>
+        </is>
+      </c>
+      <c r="C749" s="5" t="inlineStr">
+        <is>
+          <t>藤枝市</t>
+        </is>
+      </c>
+      <c r="D749" s="5" t="inlineStr">
+        <is>
+          <t>藤枝順心高等学校</t>
+        </is>
+      </c>
+      <c r="E749" s="6" t="inlineStr">
+        <is>
+          <t>054-635-1311</t>
+        </is>
+      </c>
+      <c r="F749" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G749" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H749" s="8" t="n"/>
+      <c r="I749" s="9" t="n"/>
+      <c r="J749" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K749" s="8" t="n"/>
+      <c r="L749" s="9" t="n"/>
+      <c r="M749" s="10" t="inlineStr">
+        <is>
+          <t>2つのサイトで一致、公式未確認</t>
+        </is>
+      </c>
+      <c r="N749" s="11" t="inlineStr">
+        <is>
+          <t>https://www.mapion.co.jp/phonebook/M11004/22214/ILSP0000041630_ipclm/ ; https://school.js88.com/scl_h/22009310?page=9</t>
+        </is>
+      </c>
+      <c r="O749" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" s="4" t="n">
+        <v>746</v>
+      </c>
+      <c r="B750" s="5" t="inlineStr">
+        <is>
+          <t>静岡県</t>
+        </is>
+      </c>
+      <c r="C750" s="5" t="inlineStr">
+        <is>
+          <t>藤枝市</t>
+        </is>
+      </c>
+      <c r="D750" s="5" t="inlineStr">
+        <is>
+          <t>藤枝明誠高等学校</t>
+        </is>
+      </c>
+      <c r="E750" s="6" t="inlineStr">
+        <is>
+          <t>054-635-8155</t>
+        </is>
+      </c>
+      <c r="F750" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G750" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H750" s="8" t="n"/>
+      <c r="I750" s="9" t="n"/>
+      <c r="J750" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K750" s="8" t="n"/>
+      <c r="L750" s="9" t="n"/>
+      <c r="M750" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトの事務室の番号</t>
+        </is>
+      </c>
+      <c r="N750" s="11" t="inlineStr">
+        <is>
+          <t>https://www.fgmeisei.ed.jp/contact/</t>
+        </is>
+      </c>
+      <c r="O750" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" s="4" t="n">
+        <v>747</v>
+      </c>
+      <c r="B751" s="5" t="inlineStr">
+        <is>
+          <t>静岡県</t>
+        </is>
+      </c>
+      <c r="C751" s="5" t="inlineStr">
+        <is>
+          <t>裾野市</t>
+        </is>
+      </c>
+      <c r="D751" s="5" t="inlineStr">
+        <is>
+          <t>不二聖心女子学院高等学校</t>
+        </is>
+      </c>
+      <c r="E751" s="6" t="inlineStr">
+        <is>
+          <t>055-992-0213</t>
+        </is>
+      </c>
+      <c r="F751" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G751" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H751" s="8" t="n"/>
+      <c r="I751" s="9" t="n"/>
+      <c r="J751" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K751" s="8" t="n"/>
+      <c r="L751" s="9" t="n"/>
+      <c r="M751" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認。中高共通</t>
+        </is>
+      </c>
+      <c r="N751" s="11" t="inlineStr">
+        <is>
+          <t>https://www.fujiseishin-jh.ed.jp/access/</t>
+        </is>
+      </c>
+      <c r="O751" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" s="4" t="n">
+        <v>748</v>
+      </c>
+      <c r="B752" s="5" t="inlineStr">
+        <is>
+          <t>静岡県</t>
+        </is>
+      </c>
+      <c r="C752" s="5" t="inlineStr">
+        <is>
+          <t>焼津市</t>
+        </is>
+      </c>
+      <c r="D752" s="5" t="inlineStr">
+        <is>
+          <t>焼津高等学校</t>
+        </is>
+      </c>
+      <c r="E752" s="6" t="inlineStr">
+        <is>
+          <t>054-628-7235</t>
+        </is>
+      </c>
+      <c r="F752" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G752" s="5" t="inlineStr">
+        <is>
+          <t>総合学科</t>
+        </is>
+      </c>
+      <c r="H752" s="8" t="n"/>
+      <c r="I752" s="9" t="n"/>
+      <c r="J752" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K752" s="8" t="n"/>
+      <c r="L752" s="9" t="n"/>
+      <c r="M752" s="10" t="inlineStr">
+        <is>
+          <t>私立（学校法人松薫学園）。公式サイトで確認</t>
+        </is>
+      </c>
+      <c r="N752" s="11" t="inlineStr">
+        <is>
+          <t>https://yaizu-h.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O752" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:O709"/>
-  <conditionalFormatting sqref="A5:O709">
+  <autoFilter ref="A4:O752"/>
+  <conditionalFormatting sqref="A5:O752">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$J5="アポ獲得"</formula>
     </cfRule>
@@ -42238,10 +44775,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="J5:J709" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J5:J752" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未架電,不在・折返し待ち,担当者不在,資料送付,アポ獲得,検討中,NG,番号不明"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H709 K5:K709" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="日付" error="日付で入力してください（例：2026/10/9）" type="date" operator="greaterThan">
+    <dataValidation sqref="H5:H752 K5:K752" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="日付" error="日付で入力してください（例：2026/10/9）" type="date" operator="greaterThan">
       <formula1>36526</formula1>
     </dataValidation>
   </dataValidations>
@@ -42951,6 +45488,49 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O707" r:id="rId703"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O708" r:id="rId704"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O709" r:id="rId705"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O710" r:id="rId706"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O711" r:id="rId707"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O712" r:id="rId708"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O713" r:id="rId709"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O714" r:id="rId710"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O715" r:id="rId711"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O716" r:id="rId712"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O717" r:id="rId713"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O718" r:id="rId714"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O719" r:id="rId715"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O720" r:id="rId716"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O721" r:id="rId717"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O722" r:id="rId718"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O723" r:id="rId719"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O724" r:id="rId720"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O725" r:id="rId721"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O726" r:id="rId722"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O727" r:id="rId723"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O728" r:id="rId724"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O729" r:id="rId725"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O730" r:id="rId726"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O731" r:id="rId727"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O732" r:id="rId728"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O733" r:id="rId729"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O734" r:id="rId730"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O735" r:id="rId731"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O736" r:id="rId732"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O737" r:id="rId733"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O738" r:id="rId734"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O739" r:id="rId735"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O740" r:id="rId736"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O741" r:id="rId737"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O742" r:id="rId738"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O743" r:id="rId739"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O744" r:id="rId740"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O745" r:id="rId741"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O746" r:id="rId742"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O747" r:id="rId743"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O748" r:id="rId744"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O749" r:id="rId745"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O750" r:id="rId746"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O751" r:id="rId747"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O752" r:id="rId748"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -42963,7 +45543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -43050,43 +45630,43 @@
         </is>
       </c>
       <c r="B4" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$709,A4)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$752,A4)</f>
         <v/>
       </c>
       <c r="C4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,A4,'架電リスト'!$E$5:$E$709,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,A4,'架電リスト'!$E$5:$E$752,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D4" s="16">
-        <f>B4-COUNTIFS('架電リスト'!$B$5:$B$709,A4,'架電リスト'!$J$5:$J$709,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$709,A4,'架電リスト'!$J$5:$J$709,"")</f>
+        <f>B4-COUNTIFS('架電リスト'!$B$5:$B$752,A4,'架電リスト'!$J$5:$J$752,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$752,A4,'架電リスト'!$J$5:$J$752,"")</f>
         <v/>
       </c>
       <c r="E4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A4,'架電リスト'!$J$5:$J$709,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A4,'架電リスト'!$J$5:$J$752,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A4,'架電リスト'!$J$5:$J$709,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A4,'架電リスト'!$J$5:$J$752,"担当者不在")</f>
         <v/>
       </c>
       <c r="G4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A4,'架電リスト'!$J$5:$J$709,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A4,'架電リスト'!$J$5:$J$752,"資料送付")</f>
         <v/>
       </c>
       <c r="H4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A4,'架電リスト'!$J$5:$J$709,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A4,'架電リスト'!$J$5:$J$752,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A4,'架電リスト'!$J$5:$J$709,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A4,'架電リスト'!$J$5:$J$752,"検討中")</f>
         <v/>
       </c>
       <c r="J4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A4,'架電リスト'!$J$5:$J$709,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A4,'架電リスト'!$J$5:$J$752,"NG")</f>
         <v/>
       </c>
       <c r="K4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A4,'架電リスト'!$J$5:$J$709,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A4,'架電リスト'!$J$5:$J$752,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -43097,43 +45677,43 @@
         </is>
       </c>
       <c r="B5" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$709,A5)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$752,A5)</f>
         <v/>
       </c>
       <c r="C5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,A5,'架電リスト'!$E$5:$E$709,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,A5,'架電リスト'!$E$5:$E$752,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D5" s="16">
-        <f>B5-COUNTIFS('架電リスト'!$B$5:$B$709,A5,'架電リスト'!$J$5:$J$709,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$709,A5,'架電リスト'!$J$5:$J$709,"")</f>
+        <f>B5-COUNTIFS('架電リスト'!$B$5:$B$752,A5,'架電リスト'!$J$5:$J$752,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$752,A5,'架電リスト'!$J$5:$J$752,"")</f>
         <v/>
       </c>
       <c r="E5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A5,'架電リスト'!$J$5:$J$709,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A5,'架電リスト'!$J$5:$J$752,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A5,'架電リスト'!$J$5:$J$709,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A5,'架電リスト'!$J$5:$J$752,"担当者不在")</f>
         <v/>
       </c>
       <c r="G5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A5,'架電リスト'!$J$5:$J$709,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A5,'架電リスト'!$J$5:$J$752,"資料送付")</f>
         <v/>
       </c>
       <c r="H5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A5,'架電リスト'!$J$5:$J$709,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A5,'架電リスト'!$J$5:$J$752,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A5,'架電リスト'!$J$5:$J$709,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A5,'架電リスト'!$J$5:$J$752,"検討中")</f>
         <v/>
       </c>
       <c r="J5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A5,'架電リスト'!$J$5:$J$709,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A5,'架電リスト'!$J$5:$J$752,"NG")</f>
         <v/>
       </c>
       <c r="K5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A5,'架電リスト'!$J$5:$J$709,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A5,'架電リスト'!$J$5:$J$752,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -43144,43 +45724,43 @@
         </is>
       </c>
       <c r="B6" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$709,A6)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$752,A6)</f>
         <v/>
       </c>
       <c r="C6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,A6,'架電リスト'!$E$5:$E$709,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,A6,'架電リスト'!$E$5:$E$752,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D6" s="16">
-        <f>B6-COUNTIFS('架電リスト'!$B$5:$B$709,A6,'架電リスト'!$J$5:$J$709,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$709,A6,'架電リスト'!$J$5:$J$709,"")</f>
+        <f>B6-COUNTIFS('架電リスト'!$B$5:$B$752,A6,'架電リスト'!$J$5:$J$752,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$752,A6,'架電リスト'!$J$5:$J$752,"")</f>
         <v/>
       </c>
       <c r="E6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A6,'架電リスト'!$J$5:$J$709,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A6,'架電リスト'!$J$5:$J$752,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A6,'架電リスト'!$J$5:$J$709,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A6,'架電リスト'!$J$5:$J$752,"担当者不在")</f>
         <v/>
       </c>
       <c r="G6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A6,'架電リスト'!$J$5:$J$709,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A6,'架電リスト'!$J$5:$J$752,"資料送付")</f>
         <v/>
       </c>
       <c r="H6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A6,'架電リスト'!$J$5:$J$709,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A6,'架電リスト'!$J$5:$J$752,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A6,'架電リスト'!$J$5:$J$709,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A6,'架電リスト'!$J$5:$J$752,"検討中")</f>
         <v/>
       </c>
       <c r="J6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A6,'架電リスト'!$J$5:$J$709,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A6,'架電リスト'!$J$5:$J$752,"NG")</f>
         <v/>
       </c>
       <c r="K6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A6,'架電リスト'!$J$5:$J$709,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A6,'架電リスト'!$J$5:$J$752,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -43191,43 +45771,43 @@
         </is>
       </c>
       <c r="B7" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$709,A7)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$752,A7)</f>
         <v/>
       </c>
       <c r="C7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,A7,'架電リスト'!$E$5:$E$709,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,A7,'架電リスト'!$E$5:$E$752,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D7" s="16">
-        <f>B7-COUNTIFS('架電リスト'!$B$5:$B$709,A7,'架電リスト'!$J$5:$J$709,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$709,A7,'架電リスト'!$J$5:$J$709,"")</f>
+        <f>B7-COUNTIFS('架電リスト'!$B$5:$B$752,A7,'架電リスト'!$J$5:$J$752,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$752,A7,'架電リスト'!$J$5:$J$752,"")</f>
         <v/>
       </c>
       <c r="E7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A7,'架電リスト'!$J$5:$J$709,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A7,'架電リスト'!$J$5:$J$752,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A7,'架電リスト'!$J$5:$J$709,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A7,'架電リスト'!$J$5:$J$752,"担当者不在")</f>
         <v/>
       </c>
       <c r="G7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A7,'架電リスト'!$J$5:$J$709,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A7,'架電リスト'!$J$5:$J$752,"資料送付")</f>
         <v/>
       </c>
       <c r="H7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A7,'架電リスト'!$J$5:$J$709,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A7,'架電リスト'!$J$5:$J$752,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A7,'架電リスト'!$J$5:$J$709,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A7,'架電リスト'!$J$5:$J$752,"検討中")</f>
         <v/>
       </c>
       <c r="J7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A7,'架電リスト'!$J$5:$J$709,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A7,'架電リスト'!$J$5:$J$752,"NG")</f>
         <v/>
       </c>
       <c r="K7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A7,'架電リスト'!$J$5:$J$709,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A7,'架電リスト'!$J$5:$J$752,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -43238,43 +45818,43 @@
         </is>
       </c>
       <c r="B8" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$709,A8)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$752,A8)</f>
         <v/>
       </c>
       <c r="C8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,A8,'架電リスト'!$E$5:$E$709,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,A8,'架電リスト'!$E$5:$E$752,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D8" s="16">
-        <f>B8-COUNTIFS('架電リスト'!$B$5:$B$709,A8,'架電リスト'!$J$5:$J$709,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$709,A8,'架電リスト'!$J$5:$J$709,"")</f>
+        <f>B8-COUNTIFS('架電リスト'!$B$5:$B$752,A8,'架電リスト'!$J$5:$J$752,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$752,A8,'架電リスト'!$J$5:$J$752,"")</f>
         <v/>
       </c>
       <c r="E8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A8,'架電リスト'!$J$5:$J$709,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A8,'架電リスト'!$J$5:$J$752,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A8,'架電リスト'!$J$5:$J$709,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A8,'架電リスト'!$J$5:$J$752,"担当者不在")</f>
         <v/>
       </c>
       <c r="G8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A8,'架電リスト'!$J$5:$J$709,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A8,'架電リスト'!$J$5:$J$752,"資料送付")</f>
         <v/>
       </c>
       <c r="H8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A8,'架電リスト'!$J$5:$J$709,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A8,'架電リスト'!$J$5:$J$752,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A8,'架電リスト'!$J$5:$J$709,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A8,'架電リスト'!$J$5:$J$752,"検討中")</f>
         <v/>
       </c>
       <c r="J8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A8,'架電リスト'!$J$5:$J$709,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A8,'架電リスト'!$J$5:$J$752,"NG")</f>
         <v/>
       </c>
       <c r="K8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A8,'架電リスト'!$J$5:$J$709,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A8,'架電リスト'!$J$5:$J$752,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -43285,43 +45865,43 @@
         </is>
       </c>
       <c r="B9" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$709,A9)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$752,A9)</f>
         <v/>
       </c>
       <c r="C9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,A9,'架電リスト'!$E$5:$E$709,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,A9,'架電リスト'!$E$5:$E$752,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D9" s="16">
-        <f>B9-COUNTIFS('架電リスト'!$B$5:$B$709,A9,'架電リスト'!$J$5:$J$709,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$709,A9,'架電リスト'!$J$5:$J$709,"")</f>
+        <f>B9-COUNTIFS('架電リスト'!$B$5:$B$752,A9,'架電リスト'!$J$5:$J$752,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$752,A9,'架電リスト'!$J$5:$J$752,"")</f>
         <v/>
       </c>
       <c r="E9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A9,'架電リスト'!$J$5:$J$709,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A9,'架電リスト'!$J$5:$J$752,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A9,'架電リスト'!$J$5:$J$709,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A9,'架電リスト'!$J$5:$J$752,"担当者不在")</f>
         <v/>
       </c>
       <c r="G9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A9,'架電リスト'!$J$5:$J$709,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A9,'架電リスト'!$J$5:$J$752,"資料送付")</f>
         <v/>
       </c>
       <c r="H9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A9,'架電リスト'!$J$5:$J$709,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A9,'架電リスト'!$J$5:$J$752,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A9,'架電リスト'!$J$5:$J$709,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A9,'架電リスト'!$J$5:$J$752,"検討中")</f>
         <v/>
       </c>
       <c r="J9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A9,'架電リスト'!$J$5:$J$709,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A9,'架電リスト'!$J$5:$J$752,"NG")</f>
         <v/>
       </c>
       <c r="K9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A9,'架電リスト'!$J$5:$J$709,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A9,'架電リスト'!$J$5:$J$752,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -43332,43 +45912,43 @@
         </is>
       </c>
       <c r="B10" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$709,A10)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$752,A10)</f>
         <v/>
       </c>
       <c r="C10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,A10,'架電リスト'!$E$5:$E$709,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,A10,'架電リスト'!$E$5:$E$752,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D10" s="16">
-        <f>B10-COUNTIFS('架電リスト'!$B$5:$B$709,A10,'架電リスト'!$J$5:$J$709,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$709,A10,'架電リスト'!$J$5:$J$709,"")</f>
+        <f>B10-COUNTIFS('架電リスト'!$B$5:$B$752,A10,'架電リスト'!$J$5:$J$752,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$752,A10,'架電リスト'!$J$5:$J$752,"")</f>
         <v/>
       </c>
       <c r="E10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A10,'架電リスト'!$J$5:$J$709,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A10,'架電リスト'!$J$5:$J$752,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A10,'架電リスト'!$J$5:$J$709,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A10,'架電リスト'!$J$5:$J$752,"担当者不在")</f>
         <v/>
       </c>
       <c r="G10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A10,'架電リスト'!$J$5:$J$709,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A10,'架電リスト'!$J$5:$J$752,"資料送付")</f>
         <v/>
       </c>
       <c r="H10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A10,'架電リスト'!$J$5:$J$709,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A10,'架電リスト'!$J$5:$J$752,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A10,'架電リスト'!$J$5:$J$709,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A10,'架電リスト'!$J$5:$J$752,"検討中")</f>
         <v/>
       </c>
       <c r="J10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A10,'架電リスト'!$J$5:$J$709,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A10,'架電リスト'!$J$5:$J$752,"NG")</f>
         <v/>
       </c>
       <c r="K10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A10,'架電リスト'!$J$5:$J$709,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A10,'架電リスト'!$J$5:$J$752,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -43379,43 +45959,43 @@
         </is>
       </c>
       <c r="B11" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$709,A11)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$752,A11)</f>
         <v/>
       </c>
       <c r="C11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,A11,'架電リスト'!$E$5:$E$709,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,A11,'架電リスト'!$E$5:$E$752,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D11" s="16">
-        <f>B11-COUNTIFS('架電リスト'!$B$5:$B$709,A11,'架電リスト'!$J$5:$J$709,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$709,A11,'架電リスト'!$J$5:$J$709,"")</f>
+        <f>B11-COUNTIFS('架電リスト'!$B$5:$B$752,A11,'架電リスト'!$J$5:$J$752,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$752,A11,'架電リスト'!$J$5:$J$752,"")</f>
         <v/>
       </c>
       <c r="E11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A11,'架電リスト'!$J$5:$J$709,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A11,'架電リスト'!$J$5:$J$752,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A11,'架電リスト'!$J$5:$J$709,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A11,'架電リスト'!$J$5:$J$752,"担当者不在")</f>
         <v/>
       </c>
       <c r="G11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A11,'架電リスト'!$J$5:$J$709,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A11,'架電リスト'!$J$5:$J$752,"資料送付")</f>
         <v/>
       </c>
       <c r="H11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A11,'架電リスト'!$J$5:$J$709,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A11,'架電リスト'!$J$5:$J$752,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A11,'架電リスト'!$J$5:$J$709,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A11,'架電リスト'!$J$5:$J$752,"検討中")</f>
         <v/>
       </c>
       <c r="J11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A11,'架電リスト'!$J$5:$J$709,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A11,'架電リスト'!$J$5:$J$752,"NG")</f>
         <v/>
       </c>
       <c r="K11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A11,'架電リスト'!$J$5:$J$709,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A11,'架電リスト'!$J$5:$J$752,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -43426,43 +46006,43 @@
         </is>
       </c>
       <c r="B12" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$709,A12)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$752,A12)</f>
         <v/>
       </c>
       <c r="C12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,A12,'架電リスト'!$E$5:$E$709,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,A12,'架電リスト'!$E$5:$E$752,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D12" s="16">
-        <f>B12-COUNTIFS('架電リスト'!$B$5:$B$709,A12,'架電リスト'!$J$5:$J$709,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$709,A12,'架電リスト'!$J$5:$J$709,"")</f>
+        <f>B12-COUNTIFS('架電リスト'!$B$5:$B$752,A12,'架電リスト'!$J$5:$J$752,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$752,A12,'架電リスト'!$J$5:$J$752,"")</f>
         <v/>
       </c>
       <c r="E12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A12,'架電リスト'!$J$5:$J$709,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A12,'架電リスト'!$J$5:$J$752,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A12,'架電リスト'!$J$5:$J$709,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A12,'架電リスト'!$J$5:$J$752,"担当者不在")</f>
         <v/>
       </c>
       <c r="G12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A12,'架電リスト'!$J$5:$J$709,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A12,'架電リスト'!$J$5:$J$752,"資料送付")</f>
         <v/>
       </c>
       <c r="H12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A12,'架電リスト'!$J$5:$J$709,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A12,'架電リスト'!$J$5:$J$752,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A12,'架電リスト'!$J$5:$J$709,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A12,'架電リスト'!$J$5:$J$752,"検討中")</f>
         <v/>
       </c>
       <c r="J12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A12,'架電リスト'!$J$5:$J$709,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A12,'架電リスト'!$J$5:$J$752,"NG")</f>
         <v/>
       </c>
       <c r="K12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A12,'架電リスト'!$J$5:$J$709,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A12,'架電リスト'!$J$5:$J$752,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -43473,43 +46053,43 @@
         </is>
       </c>
       <c r="B13" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$709,A13)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$752,A13)</f>
         <v/>
       </c>
       <c r="C13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,A13,'架電リスト'!$E$5:$E$709,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,A13,'架電リスト'!$E$5:$E$752,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D13" s="16">
-        <f>B13-COUNTIFS('架電リスト'!$B$5:$B$709,A13,'架電リスト'!$J$5:$J$709,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$709,A13,'架電リスト'!$J$5:$J$709,"")</f>
+        <f>B13-COUNTIFS('架電リスト'!$B$5:$B$752,A13,'架電リスト'!$J$5:$J$752,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$752,A13,'架電リスト'!$J$5:$J$752,"")</f>
         <v/>
       </c>
       <c r="E13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A13,'架電リスト'!$J$5:$J$709,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A13,'架電リスト'!$J$5:$J$752,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A13,'架電リスト'!$J$5:$J$709,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A13,'架電リスト'!$J$5:$J$752,"担当者不在")</f>
         <v/>
       </c>
       <c r="G13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A13,'架電リスト'!$J$5:$J$709,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A13,'架電リスト'!$J$5:$J$752,"資料送付")</f>
         <v/>
       </c>
       <c r="H13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A13,'架電リスト'!$J$5:$J$709,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A13,'架電リスト'!$J$5:$J$752,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A13,'架電リスト'!$J$5:$J$709,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A13,'架電リスト'!$J$5:$J$752,"検討中")</f>
         <v/>
       </c>
       <c r="J13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A13,'架電リスト'!$J$5:$J$709,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A13,'架電リスト'!$J$5:$J$752,"NG")</f>
         <v/>
       </c>
       <c r="K13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A13,'架電リスト'!$J$5:$J$709,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A13,'架電リスト'!$J$5:$J$752,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -43520,43 +46100,43 @@
         </is>
       </c>
       <c r="B14" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$709,A14)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$752,A14)</f>
         <v/>
       </c>
       <c r="C14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,A14,'架電リスト'!$E$5:$E$709,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,A14,'架電リスト'!$E$5:$E$752,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D14" s="16">
-        <f>B14-COUNTIFS('架電リスト'!$B$5:$B$709,A14,'架電リスト'!$J$5:$J$709,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$709,A14,'架電リスト'!$J$5:$J$709,"")</f>
+        <f>B14-COUNTIFS('架電リスト'!$B$5:$B$752,A14,'架電リスト'!$J$5:$J$752,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$752,A14,'架電リスト'!$J$5:$J$752,"")</f>
         <v/>
       </c>
       <c r="E14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A14,'架電リスト'!$J$5:$J$709,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A14,'架電リスト'!$J$5:$J$752,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A14,'架電リスト'!$J$5:$J$709,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A14,'架電リスト'!$J$5:$J$752,"担当者不在")</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A14,'架電リスト'!$J$5:$J$709,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A14,'架電リスト'!$J$5:$J$752,"資料送付")</f>
         <v/>
       </c>
       <c r="H14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A14,'架電リスト'!$J$5:$J$709,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A14,'架電リスト'!$J$5:$J$752,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A14,'架電リスト'!$J$5:$J$709,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A14,'架電リスト'!$J$5:$J$752,"検討中")</f>
         <v/>
       </c>
       <c r="J14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A14,'架電リスト'!$J$5:$J$709,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A14,'架電リスト'!$J$5:$J$752,"NG")</f>
         <v/>
       </c>
       <c r="K14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A14,'架電リスト'!$J$5:$J$709,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A14,'架電リスト'!$J$5:$J$752,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -43567,43 +46147,43 @@
         </is>
       </c>
       <c r="B15" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$709,A15)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$752,A15)</f>
         <v/>
       </c>
       <c r="C15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,A15,'架電リスト'!$E$5:$E$709,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,A15,'架電リスト'!$E$5:$E$752,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D15" s="16">
-        <f>B15-COUNTIFS('架電リスト'!$B$5:$B$709,A15,'架電リスト'!$J$5:$J$709,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$709,A15,'架電リスト'!$J$5:$J$709,"")</f>
+        <f>B15-COUNTIFS('架電リスト'!$B$5:$B$752,A15,'架電リスト'!$J$5:$J$752,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$752,A15,'架電リスト'!$J$5:$J$752,"")</f>
         <v/>
       </c>
       <c r="E15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A15,'架電リスト'!$J$5:$J$709,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A15,'架電リスト'!$J$5:$J$752,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A15,'架電リスト'!$J$5:$J$709,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A15,'架電リスト'!$J$5:$J$752,"担当者不在")</f>
         <v/>
       </c>
       <c r="G15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A15,'架電リスト'!$J$5:$J$709,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A15,'架電リスト'!$J$5:$J$752,"資料送付")</f>
         <v/>
       </c>
       <c r="H15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A15,'架電リスト'!$J$5:$J$709,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A15,'架電リスト'!$J$5:$J$752,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A15,'架電リスト'!$J$5:$J$709,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A15,'架電リスト'!$J$5:$J$752,"検討中")</f>
         <v/>
       </c>
       <c r="J15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A15,'架電リスト'!$J$5:$J$709,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A15,'架電リスト'!$J$5:$J$752,"NG")</f>
         <v/>
       </c>
       <c r="K15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A15,'架電リスト'!$J$5:$J$709,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A15,'架電リスト'!$J$5:$J$752,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -43614,43 +46194,43 @@
         </is>
       </c>
       <c r="B16" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$709,A16)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$752,A16)</f>
         <v/>
       </c>
       <c r="C16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,A16,'架電リスト'!$E$5:$E$709,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,A16,'架電リスト'!$E$5:$E$752,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D16" s="16">
-        <f>B16-COUNTIFS('架電リスト'!$B$5:$B$709,A16,'架電リスト'!$J$5:$J$709,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$709,A16,'架電リスト'!$J$5:$J$709,"")</f>
+        <f>B16-COUNTIFS('架電リスト'!$B$5:$B$752,A16,'架電リスト'!$J$5:$J$752,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$752,A16,'架電リスト'!$J$5:$J$752,"")</f>
         <v/>
       </c>
       <c r="E16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A16,'架電リスト'!$J$5:$J$709,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A16,'架電リスト'!$J$5:$J$752,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A16,'架電リスト'!$J$5:$J$709,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A16,'架電リスト'!$J$5:$J$752,"担当者不在")</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A16,'架電リスト'!$J$5:$J$709,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A16,'架電リスト'!$J$5:$J$752,"資料送付")</f>
         <v/>
       </c>
       <c r="H16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A16,'架電リスト'!$J$5:$J$709,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A16,'架電リスト'!$J$5:$J$752,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A16,'架電リスト'!$J$5:$J$709,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A16,'架電リスト'!$J$5:$J$752,"検討中")</f>
         <v/>
       </c>
       <c r="J16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A16,'架電リスト'!$J$5:$J$709,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A16,'架電リスト'!$J$5:$J$752,"NG")</f>
         <v/>
       </c>
       <c r="K16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A16,'架電リスト'!$J$5:$J$709,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A16,'架電リスト'!$J$5:$J$752,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -43661,43 +46241,43 @@
         </is>
       </c>
       <c r="B17" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$709,A17)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$752,A17)</f>
         <v/>
       </c>
       <c r="C17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,A17,'架電リスト'!$E$5:$E$709,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,A17,'架電リスト'!$E$5:$E$752,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D17" s="16">
-        <f>B17-COUNTIFS('架電リスト'!$B$5:$B$709,A17,'架電リスト'!$J$5:$J$709,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$709,A17,'架電リスト'!$J$5:$J$709,"")</f>
+        <f>B17-COUNTIFS('架電リスト'!$B$5:$B$752,A17,'架電リスト'!$J$5:$J$752,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$752,A17,'架電リスト'!$J$5:$J$752,"")</f>
         <v/>
       </c>
       <c r="E17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A17,'架電リスト'!$J$5:$J$709,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A17,'架電リスト'!$J$5:$J$752,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A17,'架電リスト'!$J$5:$J$709,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A17,'架電リスト'!$J$5:$J$752,"担当者不在")</f>
         <v/>
       </c>
       <c r="G17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A17,'架電リスト'!$J$5:$J$709,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A17,'架電リスト'!$J$5:$J$752,"資料送付")</f>
         <v/>
       </c>
       <c r="H17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A17,'架電リスト'!$J$5:$J$709,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A17,'架電リスト'!$J$5:$J$752,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A17,'架電リスト'!$J$5:$J$709,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A17,'架電リスト'!$J$5:$J$752,"検討中")</f>
         <v/>
       </c>
       <c r="J17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A17,'架電リスト'!$J$5:$J$709,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A17,'架電リスト'!$J$5:$J$752,"NG")</f>
         <v/>
       </c>
       <c r="K17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A17,'架電リスト'!$J$5:$J$709,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A17,'架電リスト'!$J$5:$J$752,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -43708,43 +46288,43 @@
         </is>
       </c>
       <c r="B18" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$709,A18)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$752,A18)</f>
         <v/>
       </c>
       <c r="C18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,A18,'架電リスト'!$E$5:$E$709,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,A18,'架電リスト'!$E$5:$E$752,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D18" s="16">
-        <f>B18-COUNTIFS('架電リスト'!$B$5:$B$709,A18,'架電リスト'!$J$5:$J$709,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$709,A18,'架電リスト'!$J$5:$J$709,"")</f>
+        <f>B18-COUNTIFS('架電リスト'!$B$5:$B$752,A18,'架電リスト'!$J$5:$J$752,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$752,A18,'架電リスト'!$J$5:$J$752,"")</f>
         <v/>
       </c>
       <c r="E18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A18,'架電リスト'!$J$5:$J$709,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A18,'架電リスト'!$J$5:$J$752,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A18,'架電リスト'!$J$5:$J$709,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A18,'架電リスト'!$J$5:$J$752,"担当者不在")</f>
         <v/>
       </c>
       <c r="G18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A18,'架電リスト'!$J$5:$J$709,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A18,'架電リスト'!$J$5:$J$752,"資料送付")</f>
         <v/>
       </c>
       <c r="H18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A18,'架電リスト'!$J$5:$J$709,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A18,'架電リスト'!$J$5:$J$752,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A18,'架電リスト'!$J$5:$J$709,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A18,'架電リスト'!$J$5:$J$752,"検討中")</f>
         <v/>
       </c>
       <c r="J18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A18,'架電リスト'!$J$5:$J$709,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A18,'架電リスト'!$J$5:$J$752,"NG")</f>
         <v/>
       </c>
       <c r="K18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A18,'架電リスト'!$J$5:$J$709,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A18,'架電リスト'!$J$5:$J$752,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -43755,43 +46335,43 @@
         </is>
       </c>
       <c r="B19" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$709,A19)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$752,A19)</f>
         <v/>
       </c>
       <c r="C19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,A19,'架電リスト'!$E$5:$E$709,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,A19,'架電リスト'!$E$5:$E$752,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D19" s="16">
-        <f>B19-COUNTIFS('架電リスト'!$B$5:$B$709,A19,'架電リスト'!$J$5:$J$709,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$709,A19,'架電リスト'!$J$5:$J$709,"")</f>
+        <f>B19-COUNTIFS('架電リスト'!$B$5:$B$752,A19,'架電リスト'!$J$5:$J$752,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$752,A19,'架電リスト'!$J$5:$J$752,"")</f>
         <v/>
       </c>
       <c r="E19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A19,'架電リスト'!$J$5:$J$709,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A19,'架電リスト'!$J$5:$J$752,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A19,'架電リスト'!$J$5:$J$709,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A19,'架電リスト'!$J$5:$J$752,"担当者不在")</f>
         <v/>
       </c>
       <c r="G19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A19,'架電リスト'!$J$5:$J$709,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A19,'架電リスト'!$J$5:$J$752,"資料送付")</f>
         <v/>
       </c>
       <c r="H19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A19,'架電リスト'!$J$5:$J$709,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A19,'架電リスト'!$J$5:$J$752,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A19,'架電リスト'!$J$5:$J$709,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A19,'架電リスト'!$J$5:$J$752,"検討中")</f>
         <v/>
       </c>
       <c r="J19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A19,'架電リスト'!$J$5:$J$709,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A19,'架電リスト'!$J$5:$J$752,"NG")</f>
         <v/>
       </c>
       <c r="K19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A19,'架電リスト'!$J$5:$J$709,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A19,'架電リスト'!$J$5:$J$752,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -43802,43 +46382,43 @@
         </is>
       </c>
       <c r="B20" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$709,A20)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$752,A20)</f>
         <v/>
       </c>
       <c r="C20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,A20,'架電リスト'!$E$5:$E$709,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,A20,'架電リスト'!$E$5:$E$752,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D20" s="16">
-        <f>B20-COUNTIFS('架電リスト'!$B$5:$B$709,A20,'架電リスト'!$J$5:$J$709,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$709,A20,'架電リスト'!$J$5:$J$709,"")</f>
+        <f>B20-COUNTIFS('架電リスト'!$B$5:$B$752,A20,'架電リスト'!$J$5:$J$752,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$752,A20,'架電リスト'!$J$5:$J$752,"")</f>
         <v/>
       </c>
       <c r="E20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A20,'架電リスト'!$J$5:$J$709,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A20,'架電リスト'!$J$5:$J$752,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A20,'架電リスト'!$J$5:$J$709,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A20,'架電リスト'!$J$5:$J$752,"担当者不在")</f>
         <v/>
       </c>
       <c r="G20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A20,'架電リスト'!$J$5:$J$709,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A20,'架電リスト'!$J$5:$J$752,"資料送付")</f>
         <v/>
       </c>
       <c r="H20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A20,'架電リスト'!$J$5:$J$709,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A20,'架電リスト'!$J$5:$J$752,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A20,'架電リスト'!$J$5:$J$709,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A20,'架電リスト'!$J$5:$J$752,"検討中")</f>
         <v/>
       </c>
       <c r="J20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A20,'架電リスト'!$J$5:$J$709,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A20,'架電リスト'!$J$5:$J$752,"NG")</f>
         <v/>
       </c>
       <c r="K20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A20,'架電リスト'!$J$5:$J$709,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A20,'架電リスト'!$J$5:$J$752,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -43849,43 +46429,43 @@
         </is>
       </c>
       <c r="B21" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$709,A21)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$752,A21)</f>
         <v/>
       </c>
       <c r="C21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,A21,'架電リスト'!$E$5:$E$709,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,A21,'架電リスト'!$E$5:$E$752,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D21" s="16">
-        <f>B21-COUNTIFS('架電リスト'!$B$5:$B$709,A21,'架電リスト'!$J$5:$J$709,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$709,A21,'架電リスト'!$J$5:$J$709,"")</f>
+        <f>B21-COUNTIFS('架電リスト'!$B$5:$B$752,A21,'架電リスト'!$J$5:$J$752,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$752,A21,'架電リスト'!$J$5:$J$752,"")</f>
         <v/>
       </c>
       <c r="E21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A21,'架電リスト'!$J$5:$J$709,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A21,'架電リスト'!$J$5:$J$752,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A21,'架電リスト'!$J$5:$J$709,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A21,'架電リスト'!$J$5:$J$752,"担当者不在")</f>
         <v/>
       </c>
       <c r="G21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A21,'架電リスト'!$J$5:$J$709,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A21,'架電リスト'!$J$5:$J$752,"資料送付")</f>
         <v/>
       </c>
       <c r="H21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A21,'架電リスト'!$J$5:$J$709,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A21,'架電リスト'!$J$5:$J$752,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A21,'架電リスト'!$J$5:$J$709,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A21,'架電リスト'!$J$5:$J$752,"検討中")</f>
         <v/>
       </c>
       <c r="J21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A21,'架電リスト'!$J$5:$J$709,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A21,'架電リスト'!$J$5:$J$752,"NG")</f>
         <v/>
       </c>
       <c r="K21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A21,'架電リスト'!$J$5:$J$709,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A21,'架電リスト'!$J$5:$J$752,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -43896,43 +46476,43 @@
         </is>
       </c>
       <c r="B22" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$709,A22)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$752,A22)</f>
         <v/>
       </c>
       <c r="C22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,A22,'架電リスト'!$E$5:$E$709,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,A22,'架電リスト'!$E$5:$E$752,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D22" s="16">
-        <f>B22-COUNTIFS('架電リスト'!$B$5:$B$709,A22,'架電リスト'!$J$5:$J$709,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$709,A22,'架電リスト'!$J$5:$J$709,"")</f>
+        <f>B22-COUNTIFS('架電リスト'!$B$5:$B$752,A22,'架電リスト'!$J$5:$J$752,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$752,A22,'架電リスト'!$J$5:$J$752,"")</f>
         <v/>
       </c>
       <c r="E22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A22,'架電リスト'!$J$5:$J$709,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A22,'架電リスト'!$J$5:$J$752,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A22,'架電リスト'!$J$5:$J$709,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A22,'架電リスト'!$J$5:$J$752,"担当者不在")</f>
         <v/>
       </c>
       <c r="G22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A22,'架電リスト'!$J$5:$J$709,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A22,'架電リスト'!$J$5:$J$752,"資料送付")</f>
         <v/>
       </c>
       <c r="H22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A22,'架電リスト'!$J$5:$J$709,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A22,'架電リスト'!$J$5:$J$752,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A22,'架電リスト'!$J$5:$J$709,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A22,'架電リスト'!$J$5:$J$752,"検討中")</f>
         <v/>
       </c>
       <c r="J22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A22,'架電リスト'!$J$5:$J$709,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A22,'架電リスト'!$J$5:$J$752,"NG")</f>
         <v/>
       </c>
       <c r="K22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A22,'架電リスト'!$J$5:$J$709,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A22,'架電リスト'!$J$5:$J$752,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -43943,90 +46523,137 @@
         </is>
       </c>
       <c r="B23" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$709,A23)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$752,A23)</f>
         <v/>
       </c>
       <c r="C23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,A23,'架電リスト'!$E$5:$E$709,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,A23,'架電リスト'!$E$5:$E$752,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D23" s="16">
-        <f>B23-COUNTIFS('架電リスト'!$B$5:$B$709,A23,'架電リスト'!$J$5:$J$709,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$709,A23,'架電リスト'!$J$5:$J$709,"")</f>
+        <f>B23-COUNTIFS('架電リスト'!$B$5:$B$752,A23,'架電リスト'!$J$5:$J$752,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$752,A23,'架電リスト'!$J$5:$J$752,"")</f>
         <v/>
       </c>
       <c r="E23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A23,'架電リスト'!$J$5:$J$709,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A23,'架電リスト'!$J$5:$J$752,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A23,'架電リスト'!$J$5:$J$709,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A23,'架電リスト'!$J$5:$J$752,"担当者不在")</f>
         <v/>
       </c>
       <c r="G23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A23,'架電リスト'!$J$5:$J$709,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A23,'架電リスト'!$J$5:$J$752,"資料送付")</f>
         <v/>
       </c>
       <c r="H23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A23,'架電リスト'!$J$5:$J$709,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A23,'架電リスト'!$J$5:$J$752,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A23,'架電リスト'!$J$5:$J$709,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A23,'架電リスト'!$J$5:$J$752,"検討中")</f>
         <v/>
       </c>
       <c r="J23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A23,'架電リスト'!$J$5:$J$709,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A23,'架電リスト'!$J$5:$J$752,"NG")</f>
         <v/>
       </c>
       <c r="K23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$709,$A23,'架電リスト'!$J$5:$J$709,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A23,'架電リスト'!$J$5:$J$752,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="17" t="inlineStr">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>静岡県</t>
+        </is>
+      </c>
+      <c r="B24" s="16">
+        <f>COUNTIF('架電リスト'!$B$5:$B$752,A24)</f>
+        <v/>
+      </c>
+      <c r="C24" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,A24,'架電リスト'!$E$5:$E$752,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="D24" s="16">
+        <f>B24-COUNTIFS('架電リスト'!$B$5:$B$752,A24,'架電リスト'!$J$5:$J$752,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$752,A24,'架電リスト'!$J$5:$J$752,"")</f>
+        <v/>
+      </c>
+      <c r="E24" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A24,'架電リスト'!$J$5:$J$752,"不在・折返し待ち")</f>
+        <v/>
+      </c>
+      <c r="F24" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A24,'架電リスト'!$J$5:$J$752,"担当者不在")</f>
+        <v/>
+      </c>
+      <c r="G24" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A24,'架電リスト'!$J$5:$J$752,"資料送付")</f>
+        <v/>
+      </c>
+      <c r="H24" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A24,'架電リスト'!$J$5:$J$752,"アポ獲得")</f>
+        <v/>
+      </c>
+      <c r="I24" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A24,'架電リスト'!$J$5:$J$752,"検討中")</f>
+        <v/>
+      </c>
+      <c r="J24" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A24,'架電リスト'!$J$5:$J$752,"NG")</f>
+        <v/>
+      </c>
+      <c r="K24" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A24,'架電リスト'!$J$5:$J$752,"番号不明")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="17" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B24" s="17">
-        <f>SUM(B4:B23)</f>
+      <c r="B25" s="17">
+        <f>SUM(B4:B24)</f>
         <v/>
       </c>
-      <c r="C24" s="17">
-        <f>SUM(C4:C23)</f>
+      <c r="C25" s="17">
+        <f>SUM(C4:C24)</f>
         <v/>
       </c>
-      <c r="D24" s="17">
-        <f>SUM(D4:D23)</f>
+      <c r="D25" s="17">
+        <f>SUM(D4:D24)</f>
         <v/>
       </c>
-      <c r="E24" s="17">
-        <f>SUM(E4:E23)</f>
+      <c r="E25" s="17">
+        <f>SUM(E4:E24)</f>
         <v/>
       </c>
-      <c r="F24" s="17">
-        <f>SUM(F4:F23)</f>
+      <c r="F25" s="17">
+        <f>SUM(F4:F24)</f>
         <v/>
       </c>
-      <c r="G24" s="17">
-        <f>SUM(G4:G23)</f>
+      <c r="G25" s="17">
+        <f>SUM(G4:G24)</f>
         <v/>
       </c>
-      <c r="H24" s="17">
-        <f>SUM(H4:H23)</f>
+      <c r="H25" s="17">
+        <f>SUM(H4:H24)</f>
         <v/>
       </c>
-      <c r="I24" s="17">
-        <f>SUM(I4:I23)</f>
+      <c r="I25" s="17">
+        <f>SUM(I4:I24)</f>
         <v/>
       </c>
-      <c r="J24" s="17">
-        <f>SUM(J4:J23)</f>
+      <c r="J25" s="17">
+        <f>SUM(J4:J24)</f>
         <v/>
       </c>
-      <c r="K24" s="17">
-        <f>SUM(K4:K23)</f>
+      <c r="K25" s="17">
+        <f>SUM(K4:K24)</f>
         <v/>
       </c>
     </row>
@@ -44116,7 +46743,7 @@
     <row r="11">
       <c r="A11" s="19" t="inlineStr">
         <is>
-          <t>・出典：ご提供いただいた学校ネットの検索結果（私立高校・北海道・東北・関東・中部20都道県、705校）の貼り付けデータ。並び順は都道府県ごとに元データの掲載順です。</t>
+          <t>・出典：ご提供いただいた学校ネットの検索結果（私立高校・北海道・東北・関東・中部21都道県、748校）の貼り付けデータ。並び順は都道府県ごとに元データの掲載順です。</t>
         </is>
       </c>
     </row>

--- a/call-list/私立高校_架電リスト_全体（北海道〜中部）.xlsx
+++ b/call-list/私立高校_架電リスト_全体（北海道〜中部）.xlsx
@@ -12,7 +12,7 @@
     <sheet name="使い方・注意事項" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'架電リスト'!$A$4:$O$752</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'架電リスト'!$A$4:$O$807</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'架電リスト'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -573,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O752"/>
+  <dimension ref="A1:O807"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>私立高等学校 架電リスト（北海道・東北・関東・中部21都道県／748校）</t>
+          <t>私立高等学校 架電リスト（北海道・東北・関東・中部22都道県／803校）</t>
         </is>
       </c>
     </row>
@@ -44764,9 +44764,3254 @@
         </is>
       </c>
     </row>
+    <row r="753">
+      <c r="A753" s="4" t="n">
+        <v>749</v>
+      </c>
+      <c r="B753" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C753" s="5" t="inlineStr">
+        <is>
+          <t>稲沢市</t>
+        </is>
+      </c>
+      <c r="D753" s="5" t="inlineStr">
+        <is>
+          <t>愛知啓成高等学校</t>
+        </is>
+      </c>
+      <c r="E753" s="6" t="inlineStr">
+        <is>
+          <t>0587-32-5141</t>
+        </is>
+      </c>
+      <c r="F753" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G753" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H753" s="8" t="n"/>
+      <c r="I753" s="9" t="n"/>
+      <c r="J753" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K753" s="8" t="n"/>
+      <c r="L753" s="9" t="n"/>
+      <c r="M753" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認</t>
+        </is>
+      </c>
+      <c r="N753" s="11" t="inlineStr">
+        <is>
+          <t>https://keisei.ed.jp/ ; https://www.city.inazawa.aichi.jp/0000002446.html</t>
+        </is>
+      </c>
+      <c r="O753" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" s="4" t="n">
+        <v>750</v>
+      </c>
+      <c r="B754" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C754" s="5" t="inlineStr">
+        <is>
+          <t>名古屋市千種区</t>
+        </is>
+      </c>
+      <c r="D754" s="5" t="inlineStr">
+        <is>
+          <t>愛知工業大学名電高等学校</t>
+        </is>
+      </c>
+      <c r="E754" s="6" t="inlineStr">
+        <is>
+          <t>052-721-0311</t>
+        </is>
+      </c>
+      <c r="F754" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G754" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H754" s="8" t="n"/>
+      <c r="I754" s="9" t="n"/>
+      <c r="J754" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K754" s="8" t="n"/>
+      <c r="L754" s="9" t="n"/>
+      <c r="M754" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトに「代表」と記載</t>
+        </is>
+      </c>
+      <c r="N754" s="11" t="inlineStr">
+        <is>
+          <t>https://www.meiden.ed.jp/others/contact.html</t>
+        </is>
+      </c>
+      <c r="O754" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" s="4" t="n">
+        <v>751</v>
+      </c>
+      <c r="B755" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C755" s="5" t="inlineStr">
+        <is>
+          <t>名古屋市千種区</t>
+        </is>
+      </c>
+      <c r="D755" s="5" t="inlineStr">
+        <is>
+          <t>愛知高等学校</t>
+        </is>
+      </c>
+      <c r="E755" s="6" t="inlineStr">
+        <is>
+          <t>052-721-1521</t>
+        </is>
+      </c>
+      <c r="F755" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G755" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H755" s="8" t="n"/>
+      <c r="I755" s="9" t="n"/>
+      <c r="J755" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K755" s="8" t="n"/>
+      <c r="L755" s="9" t="n"/>
+      <c r="M755" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトに「代表」と記載。中高共通</t>
+        </is>
+      </c>
+      <c r="N755" s="11" t="inlineStr">
+        <is>
+          <t>https://www.aichi-h.ed.jp/hs/access/</t>
+        </is>
+      </c>
+      <c r="O755" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" s="4" t="n">
+        <v>752</v>
+      </c>
+      <c r="B756" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C756" s="5" t="inlineStr">
+        <is>
+          <t>岡崎市</t>
+        </is>
+      </c>
+      <c r="D756" s="5" t="inlineStr">
+        <is>
+          <t>愛知産業大学三河高等学校</t>
+        </is>
+      </c>
+      <c r="E756" s="6" t="inlineStr">
+        <is>
+          <t>0564-48-5211</t>
+        </is>
+      </c>
+      <c r="F756" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G756" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H756" s="8" t="n"/>
+      <c r="I756" s="9" t="n"/>
+      <c r="J756" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K756" s="8" t="n"/>
+      <c r="L756" s="9" t="n"/>
+      <c r="M756" s="10" t="inlineStr">
+        <is>
+          <t>全日制の番号（公式サイト）。通信制課程は0564-48-5230</t>
+        </is>
+      </c>
+      <c r="N756" s="11" t="inlineStr">
+        <is>
+          <t>https://www.mikawa.ed.jp/introduction/information/</t>
+        </is>
+      </c>
+      <c r="O756" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" s="4" t="n">
+        <v>753</v>
+      </c>
+      <c r="B757" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C757" s="5" t="inlineStr">
+        <is>
+          <t>名古屋市千種区</t>
+        </is>
+      </c>
+      <c r="D757" s="5" t="inlineStr">
+        <is>
+          <t>愛知淑徳高等学校</t>
+        </is>
+      </c>
+      <c r="E757" s="6" t="inlineStr">
+        <is>
+          <t>052-781-1151</t>
+        </is>
+      </c>
+      <c r="F757" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G757" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H757" s="8" t="n"/>
+      <c r="I757" s="9" t="n"/>
+      <c r="J757" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K757" s="8" t="n"/>
+      <c r="L757" s="9" t="n"/>
+      <c r="M757" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで代表番号として確認。中高共通</t>
+        </is>
+      </c>
+      <c r="N757" s="11" t="inlineStr">
+        <is>
+          <t>https://www.aichishukutoku-h.jp/contact/</t>
+        </is>
+      </c>
+      <c r="O757" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" s="4" t="n">
+        <v>754</v>
+      </c>
+      <c r="B758" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C758" s="5" t="inlineStr">
+        <is>
+          <t>名古屋市瑞穂区</t>
+        </is>
+      </c>
+      <c r="D758" s="5" t="inlineStr">
+        <is>
+          <t>愛知みずほ大学瑞穂高等学校</t>
+        </is>
+      </c>
+      <c r="E758" s="6" t="inlineStr">
+        <is>
+          <t>052-882-1811</t>
+        </is>
+      </c>
+      <c r="F758" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G758" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H758" s="8" t="n"/>
+      <c r="I758" s="9" t="n"/>
+      <c r="J758" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K758" s="8" t="n"/>
+      <c r="L758" s="9" t="n"/>
+      <c r="M758" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認</t>
+        </is>
+      </c>
+      <c r="N758" s="11" t="inlineStr">
+        <is>
+          <t>https://www.aichi-mizuho.ac.jp/mhs/</t>
+        </is>
+      </c>
+      <c r="O758" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" s="4" t="n">
+        <v>755</v>
+      </c>
+      <c r="B759" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C759" s="5" t="inlineStr">
+        <is>
+          <t>弥富市</t>
+        </is>
+      </c>
+      <c r="D759" s="5" t="inlineStr">
+        <is>
+          <t>愛知黎明高等学校</t>
+        </is>
+      </c>
+      <c r="E759" s="6" t="inlineStr">
+        <is>
+          <t>0567-68-2233</t>
+        </is>
+      </c>
+      <c r="F759" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G759" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H759" s="8" t="n"/>
+      <c r="I759" s="9" t="n"/>
+      <c r="J759" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K759" s="8" t="n"/>
+      <c r="L759" s="9" t="n"/>
+      <c r="M759" s="10" t="inlineStr">
+        <is>
+          <t>複数サイトで一致、公式未確認。定時制あり</t>
+        </is>
+      </c>
+      <c r="N759" s="11" t="inlineStr">
+        <is>
+          <t>https://www.mapion.co.jp/phonebook/M11004/23235/ILSP0000040620_ipclm/ ; https://school.js88.com/scl_h/22011520</t>
+        </is>
+      </c>
+      <c r="O759" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" s="4" t="n">
+        <v>756</v>
+      </c>
+      <c r="B760" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C760" s="5" t="inlineStr">
+        <is>
+          <t>安城市</t>
+        </is>
+      </c>
+      <c r="D760" s="5" t="inlineStr">
+        <is>
+          <t>安城学園高等学校</t>
+        </is>
+      </c>
+      <c r="E760" s="6" t="inlineStr">
+        <is>
+          <t>0566-76-5105</t>
+        </is>
+      </c>
+      <c r="F760" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G760" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H760" s="8" t="n"/>
+      <c r="I760" s="9" t="n"/>
+      <c r="J760" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K760" s="8" t="n"/>
+      <c r="L760" s="9" t="n"/>
+      <c r="M760" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認。法人本部（0566-77-7788）とは別</t>
+        </is>
+      </c>
+      <c r="N760" s="11" t="inlineStr">
+        <is>
+          <t>https://www.angaku.jp/contact</t>
+        </is>
+      </c>
+      <c r="O760" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" s="4" t="n">
+        <v>757</v>
+      </c>
+      <c r="B761" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C761" s="5" t="inlineStr">
+        <is>
+          <t>長久手市</t>
+        </is>
+      </c>
+      <c r="D761" s="5" t="inlineStr">
+        <is>
+          <t>栄徳高等学校</t>
+        </is>
+      </c>
+      <c r="E761" s="6" t="inlineStr">
+        <is>
+          <t>0561-62-5000</t>
+        </is>
+      </c>
+      <c r="F761" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G761" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H761" s="8" t="n"/>
+      <c r="I761" s="9" t="n"/>
+      <c r="J761" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K761" s="8" t="n"/>
+      <c r="L761" s="9" t="n"/>
+      <c r="M761" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトに「代表」と記載</t>
+        </is>
+      </c>
+      <c r="N761" s="11" t="inlineStr">
+        <is>
+          <t>https://www.eitoku-h.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O761" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" s="4" t="n">
+        <v>758</v>
+      </c>
+      <c r="B762" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C762" s="5" t="inlineStr">
+        <is>
+          <t>名古屋市昭和区</t>
+        </is>
+      </c>
+      <c r="D762" s="5" t="inlineStr">
+        <is>
+          <t>桜花学園高等学校</t>
+        </is>
+      </c>
+      <c r="E762" s="6" t="inlineStr">
+        <is>
+          <t>052-741-1221</t>
+        </is>
+      </c>
+      <c r="F762" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G762" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H762" s="8" t="n"/>
+      <c r="I762" s="9" t="n"/>
+      <c r="J762" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K762" s="8" t="n"/>
+      <c r="L762" s="9" t="n"/>
+      <c r="M762" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認</t>
+        </is>
+      </c>
+      <c r="N762" s="11" t="inlineStr">
+        <is>
+          <t>https://ohka-hs.com/profile/</t>
+        </is>
+      </c>
+      <c r="O762" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" s="4" t="n">
+        <v>759</v>
+      </c>
+      <c r="B763" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C763" s="5" t="inlineStr">
+        <is>
+          <t>岡崎市</t>
+        </is>
+      </c>
+      <c r="D763" s="5" t="inlineStr">
+        <is>
+          <t>岡崎城西高等学校</t>
+        </is>
+      </c>
+      <c r="E763" s="6" t="inlineStr">
+        <is>
+          <t>0564-31-4165</t>
+        </is>
+      </c>
+      <c r="F763" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G763" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H763" s="8" t="n"/>
+      <c r="I763" s="9" t="n"/>
+      <c r="J763" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K763" s="8" t="n"/>
+      <c r="L763" s="9" t="n"/>
+      <c r="M763" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認（安城学園岡崎城西）</t>
+        </is>
+      </c>
+      <c r="N763" s="11" t="inlineStr">
+        <is>
+          <t>https://www.johsei.jp/contact/</t>
+        </is>
+      </c>
+      <c r="O763" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" s="4" t="n">
+        <v>760</v>
+      </c>
+      <c r="B764" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C764" s="5" t="inlineStr">
+        <is>
+          <t>名古屋市守山区</t>
+        </is>
+      </c>
+      <c r="D764" s="5" t="inlineStr">
+        <is>
+          <t>菊華高等学校</t>
+        </is>
+      </c>
+      <c r="E764" s="6" t="inlineStr">
+        <is>
+          <t>052-791-8261</t>
+        </is>
+      </c>
+      <c r="F764" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G764" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H764" s="8" t="n"/>
+      <c r="I764" s="9" t="n"/>
+      <c r="J764" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K764" s="8" t="n"/>
+      <c r="L764" s="9" t="n"/>
+      <c r="M764" s="10" t="inlineStr">
+        <is>
+          <t>全日制の本校の番号（公式サイト）</t>
+        </is>
+      </c>
+      <c r="N764" s="11" t="inlineStr">
+        <is>
+          <t>https://kikuka.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O764" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" s="4" t="n">
+        <v>761</v>
+      </c>
+      <c r="B765" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C765" s="5" t="inlineStr">
+        <is>
+          <t>名古屋市瑞穂区</t>
+        </is>
+      </c>
+      <c r="D765" s="5" t="inlineStr">
+        <is>
+          <t>享栄高等学校</t>
+        </is>
+      </c>
+      <c r="E765" s="6" t="inlineStr">
+        <is>
+          <t>052-841-8151</t>
+        </is>
+      </c>
+      <c r="F765" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G765" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H765" s="8" t="n"/>
+      <c r="I765" s="9" t="n"/>
+      <c r="J765" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K765" s="8" t="n"/>
+      <c r="L765" s="9" t="n"/>
+      <c r="M765" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトに「代表」と記載</t>
+        </is>
+      </c>
+      <c r="N765" s="11" t="inlineStr">
+        <is>
+          <t>https://www.kyoei-h.ed.jp/contact/</t>
+        </is>
+      </c>
+      <c r="O765" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" s="4" t="n">
+        <v>762</v>
+      </c>
+      <c r="B766" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C766" s="5" t="inlineStr">
+        <is>
+          <t>名古屋市東区</t>
+        </is>
+      </c>
+      <c r="D766" s="5" t="inlineStr">
+        <is>
+          <t>金城学院高等学校</t>
+        </is>
+      </c>
+      <c r="E766" s="6" t="inlineStr">
+        <is>
+          <t>052-931-6236</t>
+        </is>
+      </c>
+      <c r="F766" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G766" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H766" s="8" t="n"/>
+      <c r="I766" s="9" t="n"/>
+      <c r="J766" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K766" s="8" t="n"/>
+      <c r="L766" s="9" t="n"/>
+      <c r="M766" s="10" t="inlineStr">
+        <is>
+          <t>高校の番号（公式サイト）。中学校は052-931-0821、大学は別番号</t>
+        </is>
+      </c>
+      <c r="N766" s="11" t="inlineStr">
+        <is>
+          <t>https://www.hs.kinjo-u.ac.jp/contact/</t>
+        </is>
+      </c>
+      <c r="O766" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" s="4" t="n">
+        <v>763</v>
+      </c>
+      <c r="B767" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C767" s="5" t="inlineStr">
+        <is>
+          <t>名古屋市西区</t>
+        </is>
+      </c>
+      <c r="D767" s="5" t="inlineStr">
+        <is>
+          <t>啓明学館高等学校</t>
+        </is>
+      </c>
+      <c r="E767" s="6" t="inlineStr">
+        <is>
+          <t>052-571-2561</t>
+        </is>
+      </c>
+      <c r="F767" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G767" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H767" s="8" t="n"/>
+      <c r="I767" s="9" t="n"/>
+      <c r="J767" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K767" s="8" t="n"/>
+      <c r="L767" s="9" t="n"/>
+      <c r="M767" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトの事務所の番号（「代表」の表記なし）。職員室は052-571-7366</t>
+        </is>
+      </c>
+      <c r="N767" s="11" t="inlineStr">
+        <is>
+          <t>https://keimeigakkan-h.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O767" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" s="4" t="n">
+        <v>764</v>
+      </c>
+      <c r="B768" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C768" s="5" t="inlineStr">
+        <is>
+          <t>豊橋市</t>
+        </is>
+      </c>
+      <c r="D768" s="5" t="inlineStr">
+        <is>
+          <t>桜丘高等学校（愛知県）</t>
+        </is>
+      </c>
+      <c r="E768" s="6" t="inlineStr">
+        <is>
+          <t>0570-039-396</t>
+        </is>
+      </c>
+      <c r="F768" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G768" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H768" s="8" t="n"/>
+      <c r="I768" s="9" t="n"/>
+      <c r="J768" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K768" s="8" t="n"/>
+      <c r="L768" s="9" t="n"/>
+      <c r="M768" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトのナビダイヤル（学園・高校共通、通話料がかかる番号）。旧番号0532-61-6421が一部サイトに残る</t>
+        </is>
+      </c>
+      <c r="N768" s="11" t="inlineStr">
+        <is>
+          <t>https://www.sakuragaoka-gakuen.ed.jp/h/</t>
+        </is>
+      </c>
+      <c r="O768" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" s="4" t="n">
+        <v>765</v>
+      </c>
+      <c r="B769" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C769" s="5" t="inlineStr">
+        <is>
+          <t>名古屋市東区</t>
+        </is>
+      </c>
+      <c r="D769" s="5" t="inlineStr">
+        <is>
+          <t>至学館高等学校</t>
+        </is>
+      </c>
+      <c r="E769" s="6" t="inlineStr">
+        <is>
+          <t>052-723-0851</t>
+        </is>
+      </c>
+      <c r="F769" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G769" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H769" s="8" t="n"/>
+      <c r="I769" s="9" t="n"/>
+      <c r="J769" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K769" s="8" t="n"/>
+      <c r="L769" s="9" t="n"/>
+      <c r="M769" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認</t>
+        </is>
+      </c>
+      <c r="N769" s="11" t="inlineStr">
+        <is>
+          <t>https://www.shigakukan-h.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O769" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" s="4" t="n">
+        <v>766</v>
+      </c>
+      <c r="B770" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C770" s="5" t="inlineStr">
+        <is>
+          <t>一宮市</t>
+        </is>
+      </c>
+      <c r="D770" s="5" t="inlineStr">
+        <is>
+          <t>修文学院高等学校</t>
+        </is>
+      </c>
+      <c r="E770" s="6" t="inlineStr">
+        <is>
+          <t>0586-45-2102</t>
+        </is>
+      </c>
+      <c r="F770" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G770" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H770" s="8" t="n"/>
+      <c r="I770" s="9" t="n"/>
+      <c r="J770" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K770" s="8" t="n"/>
+      <c r="L770" s="9" t="n"/>
+      <c r="M770" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認。【校名変更】2022年に修文女子高校から改称・共学化</t>
+        </is>
+      </c>
+      <c r="N770" s="11" t="inlineStr">
+        <is>
+          <t>https://www.gakuin-hs.shubun.ac.jp/contact</t>
+        </is>
+      </c>
+      <c r="O770" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" s="4" t="n">
+        <v>767</v>
+      </c>
+      <c r="B771" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C771" s="5" t="inlineStr">
+        <is>
+          <t>名古屋市千種区</t>
+        </is>
+      </c>
+      <c r="D771" s="5" t="inlineStr">
+        <is>
+          <t>椙山女学園高等学校</t>
+        </is>
+      </c>
+      <c r="E771" s="6" t="inlineStr">
+        <is>
+          <t>052-751-8131</t>
+        </is>
+      </c>
+      <c r="F771" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G771" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H771" s="8" t="n"/>
+      <c r="I771" s="9" t="n"/>
+      <c r="J771" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K771" s="8" t="n"/>
+      <c r="L771" s="9" t="n"/>
+      <c r="M771" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトに「代表」と記載</t>
+        </is>
+      </c>
+      <c r="N771" s="11" t="inlineStr">
+        <is>
+          <t>https://www.sugiyama-u.ac.jp/high/index.html</t>
+        </is>
+      </c>
+      <c r="O771" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" s="4" t="n">
+        <v>768</v>
+      </c>
+      <c r="B772" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C772" s="5" t="inlineStr">
+        <is>
+          <t>瀬戸市</t>
+        </is>
+      </c>
+      <c r="D772" s="5" t="inlineStr">
+        <is>
+          <t>聖カピタニオ女子高等学校</t>
+        </is>
+      </c>
+      <c r="E772" s="6" t="inlineStr">
+        <is>
+          <t>0561-82-7711</t>
+        </is>
+      </c>
+      <c r="F772" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G772" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H772" s="8" t="n"/>
+      <c r="I772" s="9" t="n"/>
+      <c r="J772" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K772" s="8" t="n"/>
+      <c r="L772" s="9" t="n"/>
+      <c r="M772" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認</t>
+        </is>
+      </c>
+      <c r="N772" s="11" t="inlineStr">
+        <is>
+          <t>https://www.st-capitanio.ed.jp/access/access.html</t>
+        </is>
+      </c>
+      <c r="O772" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" s="4" t="n">
+        <v>769</v>
+      </c>
+      <c r="B773" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C773" s="5" t="inlineStr">
+        <is>
+          <t>扶桑町</t>
+        </is>
+      </c>
+      <c r="D773" s="5" t="inlineStr">
+        <is>
+          <t>誠信高等学校</t>
+        </is>
+      </c>
+      <c r="E773" s="6" t="inlineStr">
+        <is>
+          <t>0587-93-5380</t>
+        </is>
+      </c>
+      <c r="F773" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G773" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H773" s="8" t="n"/>
+      <c r="I773" s="9" t="n"/>
+      <c r="J773" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K773" s="8" t="n"/>
+      <c r="L773" s="9" t="n"/>
+      <c r="M773" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトに「代表」と記載。0587-93-8172はFAXなので注意</t>
+        </is>
+      </c>
+      <c r="N773" s="11" t="inlineStr">
+        <is>
+          <t>https://www.a-seishin.ed.jp/contact/</t>
+        </is>
+      </c>
+      <c r="O773" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" s="4" t="n">
+        <v>770</v>
+      </c>
+      <c r="B774" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C774" s="5" t="inlineStr">
+        <is>
+          <t>豊明市</t>
+        </is>
+      </c>
+      <c r="D774" s="5" t="inlineStr">
+        <is>
+          <t>星城高等学校</t>
+        </is>
+      </c>
+      <c r="E774" s="6" t="inlineStr">
+        <is>
+          <t>0562-97-3111</t>
+        </is>
+      </c>
+      <c r="F774" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G774" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H774" s="8" t="n"/>
+      <c r="I774" s="9" t="n"/>
+      <c r="J774" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K774" s="8" t="n"/>
+      <c r="L774" s="9" t="n"/>
+      <c r="M774" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトに「代表」と記載</t>
+        </is>
+      </c>
+      <c r="N774" s="11" t="inlineStr">
+        <is>
+          <t>https://www.seijoh.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O774" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" s="4" t="n">
+        <v>771</v>
+      </c>
+      <c r="B775" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C775" s="5" t="inlineStr">
+        <is>
+          <t>愛西市</t>
+        </is>
+      </c>
+      <c r="D775" s="5" t="inlineStr">
+        <is>
+          <t>清林館高等学校</t>
+        </is>
+      </c>
+      <c r="E775" s="6" t="inlineStr">
+        <is>
+          <t>0567-28-3010</t>
+        </is>
+      </c>
+      <c r="F775" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G775" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H775" s="8" t="n"/>
+      <c r="I775" s="9" t="n"/>
+      <c r="J775" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K775" s="8" t="n"/>
+      <c r="L775" s="9" t="n"/>
+      <c r="M775" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認</t>
+        </is>
+      </c>
+      <c r="N775" s="11" t="inlineStr">
+        <is>
+          <t>https://www.seirinkan.ed.jp/high/access</t>
+        </is>
+      </c>
+      <c r="O775" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" s="4" t="n">
+        <v>772</v>
+      </c>
+      <c r="B776" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C776" s="5" t="inlineStr">
+        <is>
+          <t>瀬戸市</t>
+        </is>
+      </c>
+      <c r="D776" s="5" t="inlineStr">
+        <is>
+          <t>聖霊高等学校</t>
+        </is>
+      </c>
+      <c r="E776" s="6" t="inlineStr">
+        <is>
+          <t>0561-21-3121</t>
+        </is>
+      </c>
+      <c r="F776" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G776" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H776" s="8" t="n"/>
+      <c r="I776" s="9" t="n"/>
+      <c r="J776" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K776" s="8" t="n"/>
+      <c r="L776" s="9" t="n"/>
+      <c r="M776" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認。中高共通</t>
+        </is>
+      </c>
+      <c r="N776" s="11" t="inlineStr">
+        <is>
+          <t>https://www.seto-seirei-js.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O776" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" s="4" t="n">
+        <v>773</v>
+      </c>
+      <c r="B777" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C777" s="5" t="inlineStr">
+        <is>
+          <t>一宮市</t>
+        </is>
+      </c>
+      <c r="D777" s="5" t="inlineStr">
+        <is>
+          <t>大成高等学校（愛知県）</t>
+        </is>
+      </c>
+      <c r="E777" s="6" t="inlineStr">
+        <is>
+          <t>0586-77-9900</t>
+        </is>
+      </c>
+      <c r="F777" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G777" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H777" s="8" t="n"/>
+      <c r="I777" s="9" t="n"/>
+      <c r="J777" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K777" s="8" t="n"/>
+      <c r="L777" s="9" t="n"/>
+      <c r="M777" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトと一宮市のサイトで一致</t>
+        </is>
+      </c>
+      <c r="N777" s="11" t="inlineStr">
+        <is>
+          <t>https://www.aichi-shinwa-taisei.ed.jp/high/ ; https://www.city.ichinomiya.aichi.jp/shisetsu/hoikugakko/1008935/1009298.html</t>
+        </is>
+      </c>
+      <c r="O777" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" s="4" t="n">
+        <v>774</v>
+      </c>
+      <c r="B778" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C778" s="5" t="inlineStr">
+        <is>
+          <t>江南市</t>
+        </is>
+      </c>
+      <c r="D778" s="5" t="inlineStr">
+        <is>
+          <t>滝高等学校</t>
+        </is>
+      </c>
+      <c r="E778" s="6" t="inlineStr">
+        <is>
+          <t>0587-56-2127</t>
+        </is>
+      </c>
+      <c r="F778" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G778" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H778" s="8" t="n"/>
+      <c r="I778" s="9" t="n"/>
+      <c r="J778" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K778" s="8" t="n"/>
+      <c r="L778" s="9" t="n"/>
+      <c r="M778" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認</t>
+        </is>
+      </c>
+      <c r="N778" s="11" t="inlineStr">
+        <is>
+          <t>https://www.taki-hj.ac.jp/guide/access.html</t>
+        </is>
+      </c>
+      <c r="O778" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" s="4" t="n">
+        <v>775</v>
+      </c>
+      <c r="B779" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C779" s="5" t="inlineStr">
+        <is>
+          <t>名古屋市南区</t>
+        </is>
+      </c>
+      <c r="D779" s="5" t="inlineStr">
+        <is>
+          <t>大同大学大同高等学校</t>
+        </is>
+      </c>
+      <c r="E779" s="6" t="inlineStr">
+        <is>
+          <t>052-611-0511</t>
+        </is>
+      </c>
+      <c r="F779" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G779" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H779" s="8" t="n"/>
+      <c r="I779" s="9" t="n"/>
+      <c r="J779" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K779" s="8" t="n"/>
+      <c r="L779" s="9" t="n"/>
+      <c r="M779" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトに「代表」と記載</t>
+        </is>
+      </c>
+      <c r="N779" s="11" t="inlineStr">
+        <is>
+          <t>https://www.daido-h.ed.jp/access/</t>
+        </is>
+      </c>
+      <c r="O779" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" s="4" t="n">
+        <v>776</v>
+      </c>
+      <c r="B780" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C780" s="5" t="inlineStr">
+        <is>
+          <t>名古屋市昭和区</t>
+        </is>
+      </c>
+      <c r="D780" s="5" t="inlineStr">
+        <is>
+          <t>中京大学附属中京高等学校</t>
+        </is>
+      </c>
+      <c r="E780" s="6" t="inlineStr">
+        <is>
+          <t>052-761-5311</t>
+        </is>
+      </c>
+      <c r="F780" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G780" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H780" s="8" t="n"/>
+      <c r="I780" s="9" t="n"/>
+      <c r="J780" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K780" s="8" t="n"/>
+      <c r="L780" s="9" t="n"/>
+      <c r="M780" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトに「代表」と記載。通信制課程も同じ番号</t>
+        </is>
+      </c>
+      <c r="N780" s="11" t="inlineStr">
+        <is>
+          <t>https://www.chukyo.ed.jp/contact/</t>
+        </is>
+      </c>
+      <c r="O780" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" s="4" t="n">
+        <v>777</v>
+      </c>
+      <c r="B781" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C781" s="5" t="inlineStr">
+        <is>
+          <t>日進市</t>
+        </is>
+      </c>
+      <c r="D781" s="5" t="inlineStr">
+        <is>
+          <t>中部大学第一高等学校</t>
+        </is>
+      </c>
+      <c r="E781" s="6" t="inlineStr">
+        <is>
+          <t>0561-73-8111</t>
+        </is>
+      </c>
+      <c r="F781" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G781" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H781" s="8" t="n"/>
+      <c r="I781" s="9" t="n"/>
+      <c r="J781" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K781" s="8" t="n"/>
+      <c r="L781" s="9" t="n"/>
+      <c r="M781" s="10" t="inlineStr">
+        <is>
+          <t>2つのサイトで一致、公式未確認</t>
+        </is>
+      </c>
+      <c r="N781" s="11" t="inlineStr">
+        <is>
+          <t>https://www.mapion.co.jp/phonebook/M11004/23230/ILSP0000041881_ipclm/ ; https://www.gakkou.net/kou/view/index_303623.html</t>
+        </is>
+      </c>
+      <c r="O781" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" s="4" t="n">
+        <v>778</v>
+      </c>
+      <c r="B782" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C782" s="5" t="inlineStr">
+        <is>
+          <t>春日井市</t>
+        </is>
+      </c>
+      <c r="D782" s="5" t="inlineStr">
+        <is>
+          <t>中部大学春日丘高等学校</t>
+        </is>
+      </c>
+      <c r="E782" s="6" t="inlineStr">
+        <is>
+          <t>0568-51-1131</t>
+        </is>
+      </c>
+      <c r="F782" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G782" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H782" s="8" t="n"/>
+      <c r="I782" s="9" t="n"/>
+      <c r="J782" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K782" s="8" t="n"/>
+      <c r="L782" s="9" t="n"/>
+      <c r="M782" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認。中学校は0568-51-1115</t>
+        </is>
+      </c>
+      <c r="N782" s="11" t="inlineStr">
+        <is>
+          <t>https://www.haruhigaoka.ed.jp/senior/ ; https://www.city.kasugai.lg.jp/shisei/shisetsu/kosodate/1010552/1010560.html</t>
+        </is>
+      </c>
+      <c r="O782" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" s="4" t="n">
+        <v>779</v>
+      </c>
+      <c r="B783" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C783" s="5" t="inlineStr">
+        <is>
+          <t>新城市</t>
+        </is>
+      </c>
+      <c r="D783" s="5" t="inlineStr">
+        <is>
+          <t>黄柳野高等学校</t>
+        </is>
+      </c>
+      <c r="E783" s="6" t="inlineStr">
+        <is>
+          <t>0536-34-0330</t>
+        </is>
+      </c>
+      <c r="F783" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G783" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H783" s="8" t="n"/>
+      <c r="I783" s="9" t="n"/>
+      <c r="J783" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K783" s="8" t="n"/>
+      <c r="L783" s="9" t="n"/>
+      <c r="M783" s="10" t="inlineStr">
+        <is>
+          <t>複数サイトで一致、公式未確認</t>
+        </is>
+      </c>
+      <c r="N783" s="11" t="inlineStr">
+        <is>
+          <t>https://www.mapion.co.jp/phonebook/M11004/23221/ILSP0000041060_ipclm/ ; https://www.navitime.co.jp/poi?spot=00004-23108700184</t>
+        </is>
+      </c>
+      <c r="O783" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" s="4" t="n">
+        <v>780</v>
+      </c>
+      <c r="B784" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C784" s="5" t="inlineStr">
+        <is>
+          <t>名古屋市天白区</t>
+        </is>
+      </c>
+      <c r="D784" s="5" t="inlineStr">
+        <is>
+          <t>東海学園高等学校</t>
+        </is>
+      </c>
+      <c r="E784" s="6" t="inlineStr">
+        <is>
+          <t>052-801-6222</t>
+        </is>
+      </c>
+      <c r="F784" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G784" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H784" s="8" t="n"/>
+      <c r="I784" s="9" t="n"/>
+      <c r="J784" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K784" s="8" t="n"/>
+      <c r="L784" s="9" t="n"/>
+      <c r="M784" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認。東海高校（東区）とは別の学校</t>
+        </is>
+      </c>
+      <c r="N784" s="11" t="inlineStr">
+        <is>
+          <t>https://tokaigakuen.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O784" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" s="4" t="n">
+        <v>781</v>
+      </c>
+      <c r="B785" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C785" s="5" t="inlineStr">
+        <is>
+          <t>名古屋市東区</t>
+        </is>
+      </c>
+      <c r="D785" s="5" t="inlineStr">
+        <is>
+          <t>東海高等学校</t>
+        </is>
+      </c>
+      <c r="E785" s="6" t="inlineStr">
+        <is>
+          <t>052-936-5111</t>
+        </is>
+      </c>
+      <c r="F785" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G785" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H785" s="8" t="n"/>
+      <c r="I785" s="9" t="n"/>
+      <c r="J785" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K785" s="8" t="n"/>
+      <c r="L785" s="9" t="n"/>
+      <c r="M785" s="10" t="inlineStr">
+        <is>
+          <t>中高共通の代表（事務所）。高校の直通は052-936-5112。東海学園（天白区）とは別の学校</t>
+        </is>
+      </c>
+      <c r="N785" s="11" t="inlineStr">
+        <is>
+          <t>https://www.tokai-jh.ed.jp/profile/06.html</t>
+        </is>
+      </c>
+      <c r="O785" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" s="4" t="n">
+        <v>782</v>
+      </c>
+      <c r="B786" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C786" s="5" t="inlineStr">
+        <is>
+          <t>名古屋市名東区</t>
+        </is>
+      </c>
+      <c r="D786" s="5" t="inlineStr">
+        <is>
+          <t>東邦高等学校</t>
+        </is>
+      </c>
+      <c r="E786" s="6" t="inlineStr">
+        <is>
+          <t>052-782-1171</t>
+        </is>
+      </c>
+      <c r="F786" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G786" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H786" s="8" t="n"/>
+      <c r="I786" s="9" t="n"/>
+      <c r="J786" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K786" s="8" t="n"/>
+      <c r="L786" s="9" t="n"/>
+      <c r="M786" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトに「代表」と記載。052-782-1241は愛知東邦大学の番号</t>
+        </is>
+      </c>
+      <c r="N786" s="11" t="inlineStr">
+        <is>
+          <t>https://www.toho-h.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O786" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" s="4" t="n">
+        <v>783</v>
+      </c>
+      <c r="B787" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C787" s="5" t="inlineStr">
+        <is>
+          <t>豊田市</t>
+        </is>
+      </c>
+      <c r="D787" s="5" t="inlineStr">
+        <is>
+          <t>杜若高等学校</t>
+        </is>
+      </c>
+      <c r="E787" s="6" t="inlineStr">
+        <is>
+          <t>0565-45-5000</t>
+        </is>
+      </c>
+      <c r="F787" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G787" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H787" s="8" t="n"/>
+      <c r="I787" s="9" t="n"/>
+      <c r="J787" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K787" s="8" t="n"/>
+      <c r="L787" s="9" t="n"/>
+      <c r="M787" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認</t>
+        </is>
+      </c>
+      <c r="N787" s="11" t="inlineStr">
+        <is>
+          <t>https://www.tojaku-h.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O787" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" s="4" t="n">
+        <v>784</v>
+      </c>
+      <c r="B788" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C788" s="5" t="inlineStr">
+        <is>
+          <t>豊川市</t>
+        </is>
+      </c>
+      <c r="D788" s="5" t="inlineStr">
+        <is>
+          <t>豊川高等学校</t>
+        </is>
+      </c>
+      <c r="E788" s="6" t="inlineStr">
+        <is>
+          <t>0533-86-4121</t>
+        </is>
+      </c>
+      <c r="F788" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G788" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H788" s="8" t="n"/>
+      <c r="I788" s="9" t="n"/>
+      <c r="J788" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K788" s="8" t="n"/>
+      <c r="L788" s="9" t="n"/>
+      <c r="M788" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトに「学校代表」と記載</t>
+        </is>
+      </c>
+      <c r="N788" s="11" t="inlineStr">
+        <is>
+          <t>https://toyokawa.ed.jp/contact</t>
+        </is>
+      </c>
+      <c r="O788" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" s="4" t="n">
+        <v>785</v>
+      </c>
+      <c r="B789" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C789" s="5" t="inlineStr">
+        <is>
+          <t>豊田市</t>
+        </is>
+      </c>
+      <c r="D789" s="5" t="inlineStr">
+        <is>
+          <t>豊田大谷高等学校</t>
+        </is>
+      </c>
+      <c r="E789" s="6" t="inlineStr">
+        <is>
+          <t>0565-48-3511</t>
+        </is>
+      </c>
+      <c r="F789" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G789" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H789" s="8" t="n"/>
+      <c r="I789" s="9" t="n"/>
+      <c r="J789" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K789" s="8" t="n"/>
+      <c r="L789" s="9" t="n"/>
+      <c r="M789" s="10" t="inlineStr">
+        <is>
+          <t>2つのサイトで一致（代表として掲載）、公式未確認</t>
+        </is>
+      </c>
+      <c r="N789" s="11" t="inlineStr">
+        <is>
+          <t>https://www.navita.co.jp/s/11101207/ ; https://www.mapion.co.jp/phonebook/M11004/23211/ILSP0000041953_ipclm/</t>
+        </is>
+      </c>
+      <c r="O789" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" s="4" t="n">
+        <v>786</v>
+      </c>
+      <c r="B790" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C790" s="5" t="inlineStr">
+        <is>
+          <t>豊橋市</t>
+        </is>
+      </c>
+      <c r="D790" s="5" t="inlineStr">
+        <is>
+          <t>豊橋中央高等学校</t>
+        </is>
+      </c>
+      <c r="E790" s="6" t="inlineStr">
+        <is>
+          <t>0532-54-1301</t>
+        </is>
+      </c>
+      <c r="F790" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G790" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H790" s="8" t="n"/>
+      <c r="I790" s="9" t="n"/>
+      <c r="J790" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K790" s="8" t="n"/>
+      <c r="L790" s="9" t="n"/>
+      <c r="M790" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認</t>
+        </is>
+      </c>
+      <c r="N790" s="11" t="inlineStr">
+        <is>
+          <t>https://toyohashi-chuo.ed.jp/?page_id=53</t>
+        </is>
+      </c>
+      <c r="O790" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" s="4" t="n">
+        <v>787</v>
+      </c>
+      <c r="B791" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C791" s="5" t="inlineStr">
+        <is>
+          <t>名古屋市中村区</t>
+        </is>
+      </c>
+      <c r="D791" s="5" t="inlineStr">
+        <is>
+          <t>同朋高等学校</t>
+        </is>
+      </c>
+      <c r="E791" s="6" t="inlineStr">
+        <is>
+          <t>052-411-1159</t>
+        </is>
+      </c>
+      <c r="F791" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G791" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H791" s="8" t="n"/>
+      <c r="I791" s="9" t="n"/>
+      <c r="J791" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K791" s="8" t="n"/>
+      <c r="L791" s="9" t="n"/>
+      <c r="M791" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトの職員室の番号。入試広報室は052-411-1216。ほかの番号を載せるサイトもあり</t>
+        </is>
+      </c>
+      <c r="N791" s="11" t="inlineStr">
+        <is>
+          <t>https://www.doho-h.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O791" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" s="4" t="n">
+        <v>788</v>
+      </c>
+      <c r="B792" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C792" s="5" t="inlineStr">
+        <is>
+          <t>名古屋市瑞穂区</t>
+        </is>
+      </c>
+      <c r="D792" s="5" t="inlineStr">
+        <is>
+          <t>名古屋葵大学高等学校</t>
+        </is>
+      </c>
+      <c r="E792" s="6" t="inlineStr">
+        <is>
+          <t>052-841-8181</t>
+        </is>
+      </c>
+      <c r="F792" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G792" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H792" s="8" t="n"/>
+      <c r="I792" s="9" t="n"/>
+      <c r="J792" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K792" s="8" t="n"/>
+      <c r="L792" s="9" t="n"/>
+      <c r="M792" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認。中高共通。【校名変更】2025年4月に名古屋女子大学高校から改称</t>
+        </is>
+      </c>
+      <c r="N792" s="11" t="inlineStr">
+        <is>
+          <t>https://www.nagoya-aoi.ed.jp/contact/</t>
+        </is>
+      </c>
+      <c r="O792" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" s="4" t="n">
+        <v>789</v>
+      </c>
+      <c r="B793" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C793" s="5" t="inlineStr">
+        <is>
+          <t>名古屋市瑞穂区</t>
+        </is>
+      </c>
+      <c r="D793" s="5" t="inlineStr">
+        <is>
+          <t>名古屋大谷高等学校</t>
+        </is>
+      </c>
+      <c r="E793" s="6" t="inlineStr">
+        <is>
+          <t>052-852-1121</t>
+        </is>
+      </c>
+      <c r="F793" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G793" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H793" s="8" t="n"/>
+      <c r="I793" s="9" t="n"/>
+      <c r="J793" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K793" s="8" t="n"/>
+      <c r="L793" s="9" t="n"/>
+      <c r="M793" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認</t>
+        </is>
+      </c>
+      <c r="N793" s="11" t="inlineStr">
+        <is>
+          <t>https://nagoyaotani.owari.ac.jp/access/</t>
+        </is>
+      </c>
+      <c r="O793" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" s="4" t="n">
+        <v>790</v>
+      </c>
+      <c r="B794" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C794" s="5" t="inlineStr">
+        <is>
+          <t>名古屋市千種区</t>
+        </is>
+      </c>
+      <c r="D794" s="5" t="inlineStr">
+        <is>
+          <t>名古屋経済大学市邨高等学校</t>
+        </is>
+      </c>
+      <c r="E794" s="6" t="inlineStr">
+        <is>
+          <t>052-721-0161</t>
+        </is>
+      </c>
+      <c r="F794" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G794" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H794" s="8" t="n"/>
+      <c r="I794" s="9" t="n"/>
+      <c r="J794" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K794" s="8" t="n"/>
+      <c r="L794" s="9" t="n"/>
+      <c r="M794" s="10" t="inlineStr">
+        <is>
+          <t>公式資料に「代表」と記載</t>
+        </is>
+      </c>
+      <c r="N794" s="11" t="inlineStr">
+        <is>
+          <t>https://ichimura.ed.jp/access/</t>
+        </is>
+      </c>
+      <c r="O794" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" s="4" t="n">
+        <v>791</v>
+      </c>
+      <c r="B795" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C795" s="5" t="inlineStr">
+        <is>
+          <t>名古屋市瑞穂区</t>
+        </is>
+      </c>
+      <c r="D795" s="5" t="inlineStr">
+        <is>
+          <t>名古屋経済大学高蔵高等学校</t>
+        </is>
+      </c>
+      <c r="E795" s="6" t="inlineStr">
+        <is>
+          <t>052-853-0050</t>
+        </is>
+      </c>
+      <c r="F795" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G795" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H795" s="8" t="n"/>
+      <c r="I795" s="9" t="n"/>
+      <c r="J795" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K795" s="8" t="n"/>
+      <c r="L795" s="9" t="n"/>
+      <c r="M795" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認。中高共通</t>
+        </is>
+      </c>
+      <c r="N795" s="11" t="inlineStr">
+        <is>
+          <t>https://www.takakura-hj.info/access</t>
+        </is>
+      </c>
+      <c r="O795" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" s="4" t="n">
+        <v>792</v>
+      </c>
+      <c r="B796" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C796" s="5" t="inlineStr">
+        <is>
+          <t>名古屋市昭和区</t>
+        </is>
+      </c>
+      <c r="D796" s="5" t="inlineStr">
+        <is>
+          <t>名古屋工業高等学校</t>
+        </is>
+      </c>
+      <c r="E796" s="6" t="inlineStr">
+        <is>
+          <t>052-871-2681</t>
+        </is>
+      </c>
+      <c r="F796" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G796" s="5" t="inlineStr">
+        <is>
+          <t>専門学科</t>
+        </is>
+      </c>
+      <c r="H796" s="8" t="n"/>
+      <c r="I796" s="9" t="n"/>
+      <c r="J796" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K796" s="8" t="n"/>
+      <c r="L796" s="9" t="n"/>
+      <c r="M796" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトと愛知県私学協会の資料で一致（私立）</t>
+        </is>
+      </c>
+      <c r="N796" s="11" t="inlineStr">
+        <is>
+          <t>https://nagoya-th.ed.jp/ ; https://www.aichi-shigaku.gr.jp/guidebook2025/pageindices/index68.html</t>
+        </is>
+      </c>
+      <c r="O796" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" s="4" t="n">
+        <v>793</v>
+      </c>
+      <c r="B797" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C797" s="5" t="inlineStr">
+        <is>
+          <t>名古屋市東区</t>
+        </is>
+      </c>
+      <c r="D797" s="5" t="inlineStr">
+        <is>
+          <t>名古屋高等学校</t>
+        </is>
+      </c>
+      <c r="E797" s="6" t="inlineStr">
+        <is>
+          <t>052-721-5271</t>
+        </is>
+      </c>
+      <c r="F797" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G797" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H797" s="8" t="n"/>
+      <c r="I797" s="9" t="n"/>
+      <c r="J797" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K797" s="8" t="n"/>
+      <c r="L797" s="9" t="n"/>
+      <c r="M797" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認。052-722-2835は同窓会の番号</t>
+        </is>
+      </c>
+      <c r="N797" s="11" t="inlineStr">
+        <is>
+          <t>https://www.meigaku.ac.jp/access/</t>
+        </is>
+      </c>
+      <c r="O797" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" s="4" t="n">
+        <v>794</v>
+      </c>
+      <c r="B798" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C798" s="5" t="inlineStr">
+        <is>
+          <t>名古屋市昭和区</t>
+        </is>
+      </c>
+      <c r="D798" s="5" t="inlineStr">
+        <is>
+          <t>名古屋国際高等学校</t>
+        </is>
+      </c>
+      <c r="E798" s="6" t="inlineStr">
+        <is>
+          <t>052-858-2200</t>
+        </is>
+      </c>
+      <c r="F798" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G798" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H798" s="8" t="n"/>
+      <c r="I798" s="9" t="n"/>
+      <c r="J798" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K798" s="8" t="n"/>
+      <c r="L798" s="9" t="n"/>
+      <c r="M798" s="10" t="inlineStr">
+        <is>
+          <t>中高代表として掲載。高校の番号として052-853-5151を載せるサイトもあり食い違い</t>
+        </is>
+      </c>
+      <c r="N798" s="11" t="inlineStr">
+        <is>
+          <t>https://www.unesco-school.mext.go.jp/schools/list/nagoya-international-junior-senior-high-school/ ; https://www.aichi.sc/gakkou/kokusai/</t>
+        </is>
+      </c>
+      <c r="O798" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" s="4" t="n">
+        <v>795</v>
+      </c>
+      <c r="B799" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C799" s="5" t="inlineStr">
+        <is>
+          <t>名古屋市中区</t>
+        </is>
+      </c>
+      <c r="D799" s="5" t="inlineStr">
+        <is>
+          <t>名古屋たちばな高等学校</t>
+        </is>
+      </c>
+      <c r="E799" s="6" t="inlineStr">
+        <is>
+          <t>052-322-1911</t>
+        </is>
+      </c>
+      <c r="F799" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G799" s="5" t="inlineStr">
+        <is>
+          <t>専門学科</t>
+        </is>
+      </c>
+      <c r="H799" s="8" t="n"/>
+      <c r="I799" s="9" t="n"/>
+      <c r="J799" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K799" s="8" t="n"/>
+      <c r="L799" s="9" t="n"/>
+      <c r="M799" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認</t>
+        </is>
+      </c>
+      <c r="N799" s="11" t="inlineStr">
+        <is>
+          <t>https://tachibana-hs.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O799" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" s="4" t="n">
+        <v>796</v>
+      </c>
+      <c r="B800" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C800" s="5" t="inlineStr">
+        <is>
+          <t>名古屋市昭和区</t>
+        </is>
+      </c>
+      <c r="D800" s="5" t="inlineStr">
+        <is>
+          <t>南山高等学校 女子部</t>
+        </is>
+      </c>
+      <c r="E800" s="6" t="inlineStr">
+        <is>
+          <t>052-831-0704</t>
+        </is>
+      </c>
+      <c r="F800" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G800" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H800" s="8" t="n"/>
+      <c r="I800" s="9" t="n"/>
+      <c r="J800" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K800" s="8" t="n"/>
+      <c r="L800" s="9" t="n"/>
+      <c r="M800" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認。中高共通。男子部とは別番号</t>
+        </is>
+      </c>
+      <c r="N800" s="11" t="inlineStr">
+        <is>
+          <t>https://www.nanzan-girls.ed.jp/access.html</t>
+        </is>
+      </c>
+      <c r="O800" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" s="4" t="n">
+        <v>797</v>
+      </c>
+      <c r="B801" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C801" s="5" t="inlineStr">
+        <is>
+          <t>名古屋市昭和区</t>
+        </is>
+      </c>
+      <c r="D801" s="5" t="inlineStr">
+        <is>
+          <t>南山高等学校 男子部</t>
+        </is>
+      </c>
+      <c r="E801" s="6" t="inlineStr">
+        <is>
+          <t>052-831-6455</t>
+        </is>
+      </c>
+      <c r="F801" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G801" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H801" s="8" t="n"/>
+      <c r="I801" s="9" t="n"/>
+      <c r="J801" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K801" s="8" t="n"/>
+      <c r="L801" s="9" t="n"/>
+      <c r="M801" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認。女子部とは別番号</t>
+        </is>
+      </c>
+      <c r="N801" s="11" t="inlineStr">
+        <is>
+          <t>https://www.nanzan-boys.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O801" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" s="4" t="n">
+        <v>798</v>
+      </c>
+      <c r="B802" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C802" s="5" t="inlineStr">
+        <is>
+          <t>美浜町</t>
+        </is>
+      </c>
+      <c r="D802" s="5" t="inlineStr">
+        <is>
+          <t>日本福祉大学付属高等学校</t>
+        </is>
+      </c>
+      <c r="E802" s="6" t="inlineStr">
+        <is>
+          <t>0569-87-2311</t>
+        </is>
+      </c>
+      <c r="F802" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G802" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H802" s="8" t="n"/>
+      <c r="I802" s="9" t="n"/>
+      <c r="J802" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K802" s="8" t="n"/>
+      <c r="L802" s="9" t="n"/>
+      <c r="M802" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認。大学の代表（0569-87-2211）とは別</t>
+        </is>
+      </c>
+      <c r="N802" s="11" t="inlineStr">
+        <is>
+          <t>https://www.n-fukushi.ac.jp/koukou/</t>
+        </is>
+      </c>
+      <c r="O802" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" s="4" t="n">
+        <v>799</v>
+      </c>
+      <c r="B803" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C803" s="5" t="inlineStr">
+        <is>
+          <t>岡崎市</t>
+        </is>
+      </c>
+      <c r="D803" s="5" t="inlineStr">
+        <is>
+          <t>人間環境大学附属岡崎高等学校</t>
+        </is>
+      </c>
+      <c r="E803" s="6" t="inlineStr">
+        <is>
+          <t>0564-22-0274</t>
+        </is>
+      </c>
+      <c r="F803" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G803" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H803" s="8" t="n"/>
+      <c r="I803" s="9" t="n"/>
+      <c r="J803" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K803" s="8" t="n"/>
+      <c r="L803" s="9" t="n"/>
+      <c r="M803" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認。2022年に旧校名から改称</t>
+        </is>
+      </c>
+      <c r="N803" s="11" t="inlineStr">
+        <is>
+          <t>https://www.jinkan-okazaki.ed.jp/about/</t>
+        </is>
+      </c>
+      <c r="O803" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" s="4" t="n">
+        <v>800</v>
+      </c>
+      <c r="B804" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C804" s="5" t="inlineStr">
+        <is>
+          <t>岡崎市</t>
+        </is>
+      </c>
+      <c r="D804" s="5" t="inlineStr">
+        <is>
+          <t>光ヶ丘女子高等学校</t>
+        </is>
+      </c>
+      <c r="E804" s="6" t="inlineStr">
+        <is>
+          <t>0564-51-5651</t>
+        </is>
+      </c>
+      <c r="F804" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G804" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H804" s="8" t="n"/>
+      <c r="I804" s="9" t="n"/>
+      <c r="J804" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K804" s="8" t="n"/>
+      <c r="L804" s="9" t="n"/>
+      <c r="M804" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認</t>
+        </is>
+      </c>
+      <c r="N804" s="11" t="inlineStr">
+        <is>
+          <t>https://hikarigaoka-h.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O804" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" s="4" t="n">
+        <v>801</v>
+      </c>
+      <c r="B805" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C805" s="5" t="inlineStr">
+        <is>
+          <t>豊橋市</t>
+        </is>
+      </c>
+      <c r="D805" s="5" t="inlineStr">
+        <is>
+          <t>藤ノ花女子高等学校</t>
+        </is>
+      </c>
+      <c r="E805" s="6" t="inlineStr">
+        <is>
+          <t>0532-61-5468</t>
+        </is>
+      </c>
+      <c r="F805" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G805" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H805" s="8" t="n"/>
+      <c r="I805" s="9" t="n"/>
+      <c r="J805" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K805" s="8" t="n"/>
+      <c r="L805" s="9" t="n"/>
+      <c r="M805" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認</t>
+        </is>
+      </c>
+      <c r="N805" s="11" t="inlineStr">
+        <is>
+          <t>https://www.fujinohana-h.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O805" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" s="4" t="n">
+        <v>802</v>
+      </c>
+      <c r="B806" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C806" s="5" t="inlineStr">
+        <is>
+          <t>小牧市</t>
+        </is>
+      </c>
+      <c r="D806" s="5" t="inlineStr">
+        <is>
+          <t>誉高等学校</t>
+        </is>
+      </c>
+      <c r="E806" s="6" t="inlineStr">
+        <is>
+          <t>0568-79-7700</t>
+        </is>
+      </c>
+      <c r="F806" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G806" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H806" s="8" t="n"/>
+      <c r="I806" s="9" t="n"/>
+      <c r="J806" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K806" s="8" t="n"/>
+      <c r="L806" s="9" t="n"/>
+      <c r="M806" s="10" t="inlineStr">
+        <is>
+          <t>小牧市のサイトほかで一致、公式未確認</t>
+        </is>
+      </c>
+      <c r="N806" s="11" t="inlineStr">
+        <is>
+          <t>https://www.mapion.co.jp/phonebook/M11004/23219/ILSP0000041861_ipclm/ ; https://www.city.komaki.aichi.jp/admin/soshiki/fumei/highscool/4872.html</t>
+        </is>
+      </c>
+      <c r="O806" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" s="4" t="n">
+        <v>803</v>
+      </c>
+      <c r="B807" s="5" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="C807" s="5" t="inlineStr">
+        <is>
+          <t>名古屋市中村区</t>
+        </is>
+      </c>
+      <c r="D807" s="5" t="inlineStr">
+        <is>
+          <t>名城大学附属高等学校</t>
+        </is>
+      </c>
+      <c r="E807" s="6" t="inlineStr">
+        <is>
+          <t>052-481-7436</t>
+        </is>
+      </c>
+      <c r="F807" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G807" s="5" t="inlineStr">
+        <is>
+          <t>普通科・総合学科</t>
+        </is>
+      </c>
+      <c r="H807" s="8" t="n"/>
+      <c r="I807" s="9" t="n"/>
+      <c r="J807" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K807" s="8" t="n"/>
+      <c r="L807" s="9" t="n"/>
+      <c r="M807" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認</t>
+        </is>
+      </c>
+      <c r="N807" s="11" t="inlineStr">
+        <is>
+          <t>https://www.meijo-h.ed.jp/profile/</t>
+        </is>
+      </c>
+      <c r="O807" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:O752"/>
-  <conditionalFormatting sqref="A5:O752">
+  <autoFilter ref="A4:O807"/>
+  <conditionalFormatting sqref="A5:O807">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$J5="アポ獲得"</formula>
     </cfRule>
@@ -44775,10 +48020,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="J5:J752" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J5:J807" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未架電,不在・折返し待ち,担当者不在,資料送付,アポ獲得,検討中,NG,番号不明"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H752 K5:K752" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="日付" error="日付で入力してください（例：2026/10/9）" type="date" operator="greaterThan">
+    <dataValidation sqref="H5:H807 K5:K807" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="日付" error="日付で入力してください（例：2026/10/9）" type="date" operator="greaterThan">
       <formula1>36526</formula1>
     </dataValidation>
   </dataValidations>
@@ -45531,6 +48776,61 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O750" r:id="rId746"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O751" r:id="rId747"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O752" r:id="rId748"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O753" r:id="rId749"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O754" r:id="rId750"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O755" r:id="rId751"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O756" r:id="rId752"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O757" r:id="rId753"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O758" r:id="rId754"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O759" r:id="rId755"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O760" r:id="rId756"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O761" r:id="rId757"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O762" r:id="rId758"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O763" r:id="rId759"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O764" r:id="rId760"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O765" r:id="rId761"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O766" r:id="rId762"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O767" r:id="rId763"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O768" r:id="rId764"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O769" r:id="rId765"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O770" r:id="rId766"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O771" r:id="rId767"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O772" r:id="rId768"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O773" r:id="rId769"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O774" r:id="rId770"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O775" r:id="rId771"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O776" r:id="rId772"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O777" r:id="rId773"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O778" r:id="rId774"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O779" r:id="rId775"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O780" r:id="rId776"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O781" r:id="rId777"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O782" r:id="rId778"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O783" r:id="rId779"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O784" r:id="rId780"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O785" r:id="rId781"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O786" r:id="rId782"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O787" r:id="rId783"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O788" r:id="rId784"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O789" r:id="rId785"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O790" r:id="rId786"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O791" r:id="rId787"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O792" r:id="rId788"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O793" r:id="rId789"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O794" r:id="rId790"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O795" r:id="rId791"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O796" r:id="rId792"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O797" r:id="rId793"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O798" r:id="rId794"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O799" r:id="rId795"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O800" r:id="rId796"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O801" r:id="rId797"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O802" r:id="rId798"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O803" r:id="rId799"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O804" r:id="rId800"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O805" r:id="rId801"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O806" r:id="rId802"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O807" r:id="rId803"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -45543,7 +48843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -45630,43 +48930,43 @@
         </is>
       </c>
       <c r="B4" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$752,A4)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$807,A4)</f>
         <v/>
       </c>
       <c r="C4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,A4,'架電リスト'!$E$5:$E$752,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,A4,'架電リスト'!$E$5:$E$807,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D4" s="16">
-        <f>B4-COUNTIFS('架電リスト'!$B$5:$B$752,A4,'架電リスト'!$J$5:$J$752,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$752,A4,'架電リスト'!$J$5:$J$752,"")</f>
+        <f>B4-COUNTIFS('架電リスト'!$B$5:$B$807,A4,'架電リスト'!$J$5:$J$807,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$807,A4,'架電リスト'!$J$5:$J$807,"")</f>
         <v/>
       </c>
       <c r="E4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A4,'架電リスト'!$J$5:$J$752,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A4,'架電リスト'!$J$5:$J$807,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A4,'架電リスト'!$J$5:$J$752,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A4,'架電リスト'!$J$5:$J$807,"担当者不在")</f>
         <v/>
       </c>
       <c r="G4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A4,'架電リスト'!$J$5:$J$752,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A4,'架電リスト'!$J$5:$J$807,"資料送付")</f>
         <v/>
       </c>
       <c r="H4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A4,'架電リスト'!$J$5:$J$752,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A4,'架電リスト'!$J$5:$J$807,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A4,'架電リスト'!$J$5:$J$752,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A4,'架電リスト'!$J$5:$J$807,"検討中")</f>
         <v/>
       </c>
       <c r="J4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A4,'架電リスト'!$J$5:$J$752,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A4,'架電リスト'!$J$5:$J$807,"NG")</f>
         <v/>
       </c>
       <c r="K4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A4,'架電リスト'!$J$5:$J$752,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A4,'架電リスト'!$J$5:$J$807,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -45677,43 +48977,43 @@
         </is>
       </c>
       <c r="B5" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$752,A5)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$807,A5)</f>
         <v/>
       </c>
       <c r="C5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,A5,'架電リスト'!$E$5:$E$752,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,A5,'架電リスト'!$E$5:$E$807,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D5" s="16">
-        <f>B5-COUNTIFS('架電リスト'!$B$5:$B$752,A5,'架電リスト'!$J$5:$J$752,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$752,A5,'架電リスト'!$J$5:$J$752,"")</f>
+        <f>B5-COUNTIFS('架電リスト'!$B$5:$B$807,A5,'架電リスト'!$J$5:$J$807,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$807,A5,'架電リスト'!$J$5:$J$807,"")</f>
         <v/>
       </c>
       <c r="E5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A5,'架電リスト'!$J$5:$J$752,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A5,'架電リスト'!$J$5:$J$807,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A5,'架電リスト'!$J$5:$J$752,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A5,'架電リスト'!$J$5:$J$807,"担当者不在")</f>
         <v/>
       </c>
       <c r="G5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A5,'架電リスト'!$J$5:$J$752,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A5,'架電リスト'!$J$5:$J$807,"資料送付")</f>
         <v/>
       </c>
       <c r="H5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A5,'架電リスト'!$J$5:$J$752,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A5,'架電リスト'!$J$5:$J$807,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A5,'架電リスト'!$J$5:$J$752,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A5,'架電リスト'!$J$5:$J$807,"検討中")</f>
         <v/>
       </c>
       <c r="J5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A5,'架電リスト'!$J$5:$J$752,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A5,'架電リスト'!$J$5:$J$807,"NG")</f>
         <v/>
       </c>
       <c r="K5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A5,'架電リスト'!$J$5:$J$752,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A5,'架電リスト'!$J$5:$J$807,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -45724,43 +49024,43 @@
         </is>
       </c>
       <c r="B6" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$752,A6)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$807,A6)</f>
         <v/>
       </c>
       <c r="C6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,A6,'架電リスト'!$E$5:$E$752,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,A6,'架電リスト'!$E$5:$E$807,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D6" s="16">
-        <f>B6-COUNTIFS('架電リスト'!$B$5:$B$752,A6,'架電リスト'!$J$5:$J$752,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$752,A6,'架電リスト'!$J$5:$J$752,"")</f>
+        <f>B6-COUNTIFS('架電リスト'!$B$5:$B$807,A6,'架電リスト'!$J$5:$J$807,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$807,A6,'架電リスト'!$J$5:$J$807,"")</f>
         <v/>
       </c>
       <c r="E6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A6,'架電リスト'!$J$5:$J$752,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A6,'架電リスト'!$J$5:$J$807,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A6,'架電リスト'!$J$5:$J$752,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A6,'架電リスト'!$J$5:$J$807,"担当者不在")</f>
         <v/>
       </c>
       <c r="G6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A6,'架電リスト'!$J$5:$J$752,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A6,'架電リスト'!$J$5:$J$807,"資料送付")</f>
         <v/>
       </c>
       <c r="H6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A6,'架電リスト'!$J$5:$J$752,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A6,'架電リスト'!$J$5:$J$807,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A6,'架電リスト'!$J$5:$J$752,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A6,'架電リスト'!$J$5:$J$807,"検討中")</f>
         <v/>
       </c>
       <c r="J6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A6,'架電リスト'!$J$5:$J$752,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A6,'架電リスト'!$J$5:$J$807,"NG")</f>
         <v/>
       </c>
       <c r="K6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A6,'架電リスト'!$J$5:$J$752,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A6,'架電リスト'!$J$5:$J$807,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -45771,43 +49071,43 @@
         </is>
       </c>
       <c r="B7" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$752,A7)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$807,A7)</f>
         <v/>
       </c>
       <c r="C7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,A7,'架電リスト'!$E$5:$E$752,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,A7,'架電リスト'!$E$5:$E$807,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D7" s="16">
-        <f>B7-COUNTIFS('架電リスト'!$B$5:$B$752,A7,'架電リスト'!$J$5:$J$752,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$752,A7,'架電リスト'!$J$5:$J$752,"")</f>
+        <f>B7-COUNTIFS('架電リスト'!$B$5:$B$807,A7,'架電リスト'!$J$5:$J$807,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$807,A7,'架電リスト'!$J$5:$J$807,"")</f>
         <v/>
       </c>
       <c r="E7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A7,'架電リスト'!$J$5:$J$752,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A7,'架電リスト'!$J$5:$J$807,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A7,'架電リスト'!$J$5:$J$752,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A7,'架電リスト'!$J$5:$J$807,"担当者不在")</f>
         <v/>
       </c>
       <c r="G7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A7,'架電リスト'!$J$5:$J$752,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A7,'架電リスト'!$J$5:$J$807,"資料送付")</f>
         <v/>
       </c>
       <c r="H7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A7,'架電リスト'!$J$5:$J$752,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A7,'架電リスト'!$J$5:$J$807,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A7,'架電リスト'!$J$5:$J$752,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A7,'架電リスト'!$J$5:$J$807,"検討中")</f>
         <v/>
       </c>
       <c r="J7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A7,'架電リスト'!$J$5:$J$752,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A7,'架電リスト'!$J$5:$J$807,"NG")</f>
         <v/>
       </c>
       <c r="K7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A7,'架電リスト'!$J$5:$J$752,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A7,'架電リスト'!$J$5:$J$807,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -45818,43 +49118,43 @@
         </is>
       </c>
       <c r="B8" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$752,A8)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$807,A8)</f>
         <v/>
       </c>
       <c r="C8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,A8,'架電リスト'!$E$5:$E$752,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,A8,'架電リスト'!$E$5:$E$807,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D8" s="16">
-        <f>B8-COUNTIFS('架電リスト'!$B$5:$B$752,A8,'架電リスト'!$J$5:$J$752,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$752,A8,'架電リスト'!$J$5:$J$752,"")</f>
+        <f>B8-COUNTIFS('架電リスト'!$B$5:$B$807,A8,'架電リスト'!$J$5:$J$807,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$807,A8,'架電リスト'!$J$5:$J$807,"")</f>
         <v/>
       </c>
       <c r="E8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A8,'架電リスト'!$J$5:$J$752,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A8,'架電リスト'!$J$5:$J$807,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A8,'架電リスト'!$J$5:$J$752,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A8,'架電リスト'!$J$5:$J$807,"担当者不在")</f>
         <v/>
       </c>
       <c r="G8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A8,'架電リスト'!$J$5:$J$752,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A8,'架電リスト'!$J$5:$J$807,"資料送付")</f>
         <v/>
       </c>
       <c r="H8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A8,'架電リスト'!$J$5:$J$752,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A8,'架電リスト'!$J$5:$J$807,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A8,'架電リスト'!$J$5:$J$752,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A8,'架電リスト'!$J$5:$J$807,"検討中")</f>
         <v/>
       </c>
       <c r="J8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A8,'架電リスト'!$J$5:$J$752,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A8,'架電リスト'!$J$5:$J$807,"NG")</f>
         <v/>
       </c>
       <c r="K8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A8,'架電リスト'!$J$5:$J$752,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A8,'架電リスト'!$J$5:$J$807,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -45865,43 +49165,43 @@
         </is>
       </c>
       <c r="B9" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$752,A9)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$807,A9)</f>
         <v/>
       </c>
       <c r="C9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,A9,'架電リスト'!$E$5:$E$752,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,A9,'架電リスト'!$E$5:$E$807,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D9" s="16">
-        <f>B9-COUNTIFS('架電リスト'!$B$5:$B$752,A9,'架電リスト'!$J$5:$J$752,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$752,A9,'架電リスト'!$J$5:$J$752,"")</f>
+        <f>B9-COUNTIFS('架電リスト'!$B$5:$B$807,A9,'架電リスト'!$J$5:$J$807,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$807,A9,'架電リスト'!$J$5:$J$807,"")</f>
         <v/>
       </c>
       <c r="E9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A9,'架電リスト'!$J$5:$J$752,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A9,'架電リスト'!$J$5:$J$807,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A9,'架電リスト'!$J$5:$J$752,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A9,'架電リスト'!$J$5:$J$807,"担当者不在")</f>
         <v/>
       </c>
       <c r="G9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A9,'架電リスト'!$J$5:$J$752,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A9,'架電リスト'!$J$5:$J$807,"資料送付")</f>
         <v/>
       </c>
       <c r="H9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A9,'架電リスト'!$J$5:$J$752,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A9,'架電リスト'!$J$5:$J$807,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A9,'架電リスト'!$J$5:$J$752,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A9,'架電リスト'!$J$5:$J$807,"検討中")</f>
         <v/>
       </c>
       <c r="J9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A9,'架電リスト'!$J$5:$J$752,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A9,'架電リスト'!$J$5:$J$807,"NG")</f>
         <v/>
       </c>
       <c r="K9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A9,'架電リスト'!$J$5:$J$752,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A9,'架電リスト'!$J$5:$J$807,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -45912,43 +49212,43 @@
         </is>
       </c>
       <c r="B10" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$752,A10)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$807,A10)</f>
         <v/>
       </c>
       <c r="C10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,A10,'架電リスト'!$E$5:$E$752,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,A10,'架電リスト'!$E$5:$E$807,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D10" s="16">
-        <f>B10-COUNTIFS('架電リスト'!$B$5:$B$752,A10,'架電リスト'!$J$5:$J$752,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$752,A10,'架電リスト'!$J$5:$J$752,"")</f>
+        <f>B10-COUNTIFS('架電リスト'!$B$5:$B$807,A10,'架電リスト'!$J$5:$J$807,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$807,A10,'架電リスト'!$J$5:$J$807,"")</f>
         <v/>
       </c>
       <c r="E10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A10,'架電リスト'!$J$5:$J$752,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A10,'架電リスト'!$J$5:$J$807,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A10,'架電リスト'!$J$5:$J$752,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A10,'架電リスト'!$J$5:$J$807,"担当者不在")</f>
         <v/>
       </c>
       <c r="G10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A10,'架電リスト'!$J$5:$J$752,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A10,'架電リスト'!$J$5:$J$807,"資料送付")</f>
         <v/>
       </c>
       <c r="H10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A10,'架電リスト'!$J$5:$J$752,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A10,'架電リスト'!$J$5:$J$807,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A10,'架電リスト'!$J$5:$J$752,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A10,'架電リスト'!$J$5:$J$807,"検討中")</f>
         <v/>
       </c>
       <c r="J10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A10,'架電リスト'!$J$5:$J$752,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A10,'架電リスト'!$J$5:$J$807,"NG")</f>
         <v/>
       </c>
       <c r="K10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A10,'架電リスト'!$J$5:$J$752,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A10,'架電リスト'!$J$5:$J$807,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -45959,43 +49259,43 @@
         </is>
       </c>
       <c r="B11" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$752,A11)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$807,A11)</f>
         <v/>
       </c>
       <c r="C11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,A11,'架電リスト'!$E$5:$E$752,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,A11,'架電リスト'!$E$5:$E$807,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D11" s="16">
-        <f>B11-COUNTIFS('架電リスト'!$B$5:$B$752,A11,'架電リスト'!$J$5:$J$752,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$752,A11,'架電リスト'!$J$5:$J$752,"")</f>
+        <f>B11-COUNTIFS('架電リスト'!$B$5:$B$807,A11,'架電リスト'!$J$5:$J$807,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$807,A11,'架電リスト'!$J$5:$J$807,"")</f>
         <v/>
       </c>
       <c r="E11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A11,'架電リスト'!$J$5:$J$752,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A11,'架電リスト'!$J$5:$J$807,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A11,'架電リスト'!$J$5:$J$752,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A11,'架電リスト'!$J$5:$J$807,"担当者不在")</f>
         <v/>
       </c>
       <c r="G11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A11,'架電リスト'!$J$5:$J$752,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A11,'架電リスト'!$J$5:$J$807,"資料送付")</f>
         <v/>
       </c>
       <c r="H11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A11,'架電リスト'!$J$5:$J$752,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A11,'架電リスト'!$J$5:$J$807,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A11,'架電リスト'!$J$5:$J$752,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A11,'架電リスト'!$J$5:$J$807,"検討中")</f>
         <v/>
       </c>
       <c r="J11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A11,'架電リスト'!$J$5:$J$752,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A11,'架電リスト'!$J$5:$J$807,"NG")</f>
         <v/>
       </c>
       <c r="K11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A11,'架電リスト'!$J$5:$J$752,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A11,'架電リスト'!$J$5:$J$807,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -46006,43 +49306,43 @@
         </is>
       </c>
       <c r="B12" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$752,A12)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$807,A12)</f>
         <v/>
       </c>
       <c r="C12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,A12,'架電リスト'!$E$5:$E$752,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,A12,'架電リスト'!$E$5:$E$807,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D12" s="16">
-        <f>B12-COUNTIFS('架電リスト'!$B$5:$B$752,A12,'架電リスト'!$J$5:$J$752,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$752,A12,'架電リスト'!$J$5:$J$752,"")</f>
+        <f>B12-COUNTIFS('架電リスト'!$B$5:$B$807,A12,'架電リスト'!$J$5:$J$807,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$807,A12,'架電リスト'!$J$5:$J$807,"")</f>
         <v/>
       </c>
       <c r="E12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A12,'架電リスト'!$J$5:$J$752,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A12,'架電リスト'!$J$5:$J$807,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A12,'架電リスト'!$J$5:$J$752,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A12,'架電リスト'!$J$5:$J$807,"担当者不在")</f>
         <v/>
       </c>
       <c r="G12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A12,'架電リスト'!$J$5:$J$752,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A12,'架電リスト'!$J$5:$J$807,"資料送付")</f>
         <v/>
       </c>
       <c r="H12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A12,'架電リスト'!$J$5:$J$752,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A12,'架電リスト'!$J$5:$J$807,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A12,'架電リスト'!$J$5:$J$752,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A12,'架電リスト'!$J$5:$J$807,"検討中")</f>
         <v/>
       </c>
       <c r="J12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A12,'架電リスト'!$J$5:$J$752,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A12,'架電リスト'!$J$5:$J$807,"NG")</f>
         <v/>
       </c>
       <c r="K12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A12,'架電リスト'!$J$5:$J$752,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A12,'架電リスト'!$J$5:$J$807,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -46053,43 +49353,43 @@
         </is>
       </c>
       <c r="B13" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$752,A13)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$807,A13)</f>
         <v/>
       </c>
       <c r="C13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,A13,'架電リスト'!$E$5:$E$752,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,A13,'架電リスト'!$E$5:$E$807,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D13" s="16">
-        <f>B13-COUNTIFS('架電リスト'!$B$5:$B$752,A13,'架電リスト'!$J$5:$J$752,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$752,A13,'架電リスト'!$J$5:$J$752,"")</f>
+        <f>B13-COUNTIFS('架電リスト'!$B$5:$B$807,A13,'架電リスト'!$J$5:$J$807,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$807,A13,'架電リスト'!$J$5:$J$807,"")</f>
         <v/>
       </c>
       <c r="E13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A13,'架電リスト'!$J$5:$J$752,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A13,'架電リスト'!$J$5:$J$807,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A13,'架電リスト'!$J$5:$J$752,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A13,'架電リスト'!$J$5:$J$807,"担当者不在")</f>
         <v/>
       </c>
       <c r="G13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A13,'架電リスト'!$J$5:$J$752,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A13,'架電リスト'!$J$5:$J$807,"資料送付")</f>
         <v/>
       </c>
       <c r="H13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A13,'架電リスト'!$J$5:$J$752,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A13,'架電リスト'!$J$5:$J$807,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A13,'架電リスト'!$J$5:$J$752,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A13,'架電リスト'!$J$5:$J$807,"検討中")</f>
         <v/>
       </c>
       <c r="J13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A13,'架電リスト'!$J$5:$J$752,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A13,'架電リスト'!$J$5:$J$807,"NG")</f>
         <v/>
       </c>
       <c r="K13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A13,'架電リスト'!$J$5:$J$752,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A13,'架電リスト'!$J$5:$J$807,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -46100,43 +49400,43 @@
         </is>
       </c>
       <c r="B14" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$752,A14)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$807,A14)</f>
         <v/>
       </c>
       <c r="C14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,A14,'架電リスト'!$E$5:$E$752,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,A14,'架電リスト'!$E$5:$E$807,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D14" s="16">
-        <f>B14-COUNTIFS('架電リスト'!$B$5:$B$752,A14,'架電リスト'!$J$5:$J$752,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$752,A14,'架電リスト'!$J$5:$J$752,"")</f>
+        <f>B14-COUNTIFS('架電リスト'!$B$5:$B$807,A14,'架電リスト'!$J$5:$J$807,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$807,A14,'架電リスト'!$J$5:$J$807,"")</f>
         <v/>
       </c>
       <c r="E14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A14,'架電リスト'!$J$5:$J$752,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A14,'架電リスト'!$J$5:$J$807,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A14,'架電リスト'!$J$5:$J$752,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A14,'架電リスト'!$J$5:$J$807,"担当者不在")</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A14,'架電リスト'!$J$5:$J$752,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A14,'架電リスト'!$J$5:$J$807,"資料送付")</f>
         <v/>
       </c>
       <c r="H14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A14,'架電リスト'!$J$5:$J$752,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A14,'架電リスト'!$J$5:$J$807,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A14,'架電リスト'!$J$5:$J$752,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A14,'架電リスト'!$J$5:$J$807,"検討中")</f>
         <v/>
       </c>
       <c r="J14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A14,'架電リスト'!$J$5:$J$752,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A14,'架電リスト'!$J$5:$J$807,"NG")</f>
         <v/>
       </c>
       <c r="K14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A14,'架電リスト'!$J$5:$J$752,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A14,'架電リスト'!$J$5:$J$807,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -46147,43 +49447,43 @@
         </is>
       </c>
       <c r="B15" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$752,A15)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$807,A15)</f>
         <v/>
       </c>
       <c r="C15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,A15,'架電リスト'!$E$5:$E$752,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,A15,'架電リスト'!$E$5:$E$807,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D15" s="16">
-        <f>B15-COUNTIFS('架電リスト'!$B$5:$B$752,A15,'架電リスト'!$J$5:$J$752,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$752,A15,'架電リスト'!$J$5:$J$752,"")</f>
+        <f>B15-COUNTIFS('架電リスト'!$B$5:$B$807,A15,'架電リスト'!$J$5:$J$807,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$807,A15,'架電リスト'!$J$5:$J$807,"")</f>
         <v/>
       </c>
       <c r="E15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A15,'架電リスト'!$J$5:$J$752,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A15,'架電リスト'!$J$5:$J$807,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A15,'架電リスト'!$J$5:$J$752,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A15,'架電リスト'!$J$5:$J$807,"担当者不在")</f>
         <v/>
       </c>
       <c r="G15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A15,'架電リスト'!$J$5:$J$752,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A15,'架電リスト'!$J$5:$J$807,"資料送付")</f>
         <v/>
       </c>
       <c r="H15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A15,'架電リスト'!$J$5:$J$752,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A15,'架電リスト'!$J$5:$J$807,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A15,'架電リスト'!$J$5:$J$752,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A15,'架電リスト'!$J$5:$J$807,"検討中")</f>
         <v/>
       </c>
       <c r="J15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A15,'架電リスト'!$J$5:$J$752,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A15,'架電リスト'!$J$5:$J$807,"NG")</f>
         <v/>
       </c>
       <c r="K15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A15,'架電リスト'!$J$5:$J$752,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A15,'架電リスト'!$J$5:$J$807,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -46194,43 +49494,43 @@
         </is>
       </c>
       <c r="B16" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$752,A16)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$807,A16)</f>
         <v/>
       </c>
       <c r="C16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,A16,'架電リスト'!$E$5:$E$752,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,A16,'架電リスト'!$E$5:$E$807,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D16" s="16">
-        <f>B16-COUNTIFS('架電リスト'!$B$5:$B$752,A16,'架電リスト'!$J$5:$J$752,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$752,A16,'架電リスト'!$J$5:$J$752,"")</f>
+        <f>B16-COUNTIFS('架電リスト'!$B$5:$B$807,A16,'架電リスト'!$J$5:$J$807,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$807,A16,'架電リスト'!$J$5:$J$807,"")</f>
         <v/>
       </c>
       <c r="E16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A16,'架電リスト'!$J$5:$J$752,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A16,'架電リスト'!$J$5:$J$807,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A16,'架電リスト'!$J$5:$J$752,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A16,'架電リスト'!$J$5:$J$807,"担当者不在")</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A16,'架電リスト'!$J$5:$J$752,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A16,'架電リスト'!$J$5:$J$807,"資料送付")</f>
         <v/>
       </c>
       <c r="H16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A16,'架電リスト'!$J$5:$J$752,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A16,'架電リスト'!$J$5:$J$807,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A16,'架電リスト'!$J$5:$J$752,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A16,'架電リスト'!$J$5:$J$807,"検討中")</f>
         <v/>
       </c>
       <c r="J16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A16,'架電リスト'!$J$5:$J$752,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A16,'架電リスト'!$J$5:$J$807,"NG")</f>
         <v/>
       </c>
       <c r="K16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A16,'架電リスト'!$J$5:$J$752,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A16,'架電リスト'!$J$5:$J$807,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -46241,43 +49541,43 @@
         </is>
       </c>
       <c r="B17" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$752,A17)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$807,A17)</f>
         <v/>
       </c>
       <c r="C17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,A17,'架電リスト'!$E$5:$E$752,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,A17,'架電リスト'!$E$5:$E$807,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D17" s="16">
-        <f>B17-COUNTIFS('架電リスト'!$B$5:$B$752,A17,'架電リスト'!$J$5:$J$752,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$752,A17,'架電リスト'!$J$5:$J$752,"")</f>
+        <f>B17-COUNTIFS('架電リスト'!$B$5:$B$807,A17,'架電リスト'!$J$5:$J$807,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$807,A17,'架電リスト'!$J$5:$J$807,"")</f>
         <v/>
       </c>
       <c r="E17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A17,'架電リスト'!$J$5:$J$752,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A17,'架電リスト'!$J$5:$J$807,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A17,'架電リスト'!$J$5:$J$752,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A17,'架電リスト'!$J$5:$J$807,"担当者不在")</f>
         <v/>
       </c>
       <c r="G17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A17,'架電リスト'!$J$5:$J$752,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A17,'架電リスト'!$J$5:$J$807,"資料送付")</f>
         <v/>
       </c>
       <c r="H17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A17,'架電リスト'!$J$5:$J$752,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A17,'架電リスト'!$J$5:$J$807,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A17,'架電リスト'!$J$5:$J$752,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A17,'架電リスト'!$J$5:$J$807,"検討中")</f>
         <v/>
       </c>
       <c r="J17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A17,'架電リスト'!$J$5:$J$752,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A17,'架電リスト'!$J$5:$J$807,"NG")</f>
         <v/>
       </c>
       <c r="K17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A17,'架電リスト'!$J$5:$J$752,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A17,'架電リスト'!$J$5:$J$807,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -46288,43 +49588,43 @@
         </is>
       </c>
       <c r="B18" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$752,A18)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$807,A18)</f>
         <v/>
       </c>
       <c r="C18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,A18,'架電リスト'!$E$5:$E$752,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,A18,'架電リスト'!$E$5:$E$807,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D18" s="16">
-        <f>B18-COUNTIFS('架電リスト'!$B$5:$B$752,A18,'架電リスト'!$J$5:$J$752,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$752,A18,'架電リスト'!$J$5:$J$752,"")</f>
+        <f>B18-COUNTIFS('架電リスト'!$B$5:$B$807,A18,'架電リスト'!$J$5:$J$807,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$807,A18,'架電リスト'!$J$5:$J$807,"")</f>
         <v/>
       </c>
       <c r="E18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A18,'架電リスト'!$J$5:$J$752,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A18,'架電リスト'!$J$5:$J$807,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A18,'架電リスト'!$J$5:$J$752,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A18,'架電リスト'!$J$5:$J$807,"担当者不在")</f>
         <v/>
       </c>
       <c r="G18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A18,'架電リスト'!$J$5:$J$752,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A18,'架電リスト'!$J$5:$J$807,"資料送付")</f>
         <v/>
       </c>
       <c r="H18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A18,'架電リスト'!$J$5:$J$752,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A18,'架電リスト'!$J$5:$J$807,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A18,'架電リスト'!$J$5:$J$752,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A18,'架電リスト'!$J$5:$J$807,"検討中")</f>
         <v/>
       </c>
       <c r="J18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A18,'架電リスト'!$J$5:$J$752,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A18,'架電リスト'!$J$5:$J$807,"NG")</f>
         <v/>
       </c>
       <c r="K18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A18,'架電リスト'!$J$5:$J$752,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A18,'架電リスト'!$J$5:$J$807,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -46335,43 +49635,43 @@
         </is>
       </c>
       <c r="B19" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$752,A19)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$807,A19)</f>
         <v/>
       </c>
       <c r="C19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,A19,'架電リスト'!$E$5:$E$752,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,A19,'架電リスト'!$E$5:$E$807,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D19" s="16">
-        <f>B19-COUNTIFS('架電リスト'!$B$5:$B$752,A19,'架電リスト'!$J$5:$J$752,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$752,A19,'架電リスト'!$J$5:$J$752,"")</f>
+        <f>B19-COUNTIFS('架電リスト'!$B$5:$B$807,A19,'架電リスト'!$J$5:$J$807,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$807,A19,'架電リスト'!$J$5:$J$807,"")</f>
         <v/>
       </c>
       <c r="E19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A19,'架電リスト'!$J$5:$J$752,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A19,'架電リスト'!$J$5:$J$807,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A19,'架電リスト'!$J$5:$J$752,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A19,'架電リスト'!$J$5:$J$807,"担当者不在")</f>
         <v/>
       </c>
       <c r="G19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A19,'架電リスト'!$J$5:$J$752,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A19,'架電リスト'!$J$5:$J$807,"資料送付")</f>
         <v/>
       </c>
       <c r="H19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A19,'架電リスト'!$J$5:$J$752,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A19,'架電リスト'!$J$5:$J$807,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A19,'架電リスト'!$J$5:$J$752,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A19,'架電リスト'!$J$5:$J$807,"検討中")</f>
         <v/>
       </c>
       <c r="J19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A19,'架電リスト'!$J$5:$J$752,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A19,'架電リスト'!$J$5:$J$807,"NG")</f>
         <v/>
       </c>
       <c r="K19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A19,'架電リスト'!$J$5:$J$752,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A19,'架電リスト'!$J$5:$J$807,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -46382,43 +49682,43 @@
         </is>
       </c>
       <c r="B20" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$752,A20)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$807,A20)</f>
         <v/>
       </c>
       <c r="C20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,A20,'架電リスト'!$E$5:$E$752,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,A20,'架電リスト'!$E$5:$E$807,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D20" s="16">
-        <f>B20-COUNTIFS('架電リスト'!$B$5:$B$752,A20,'架電リスト'!$J$5:$J$752,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$752,A20,'架電リスト'!$J$5:$J$752,"")</f>
+        <f>B20-COUNTIFS('架電リスト'!$B$5:$B$807,A20,'架電リスト'!$J$5:$J$807,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$807,A20,'架電リスト'!$J$5:$J$807,"")</f>
         <v/>
       </c>
       <c r="E20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A20,'架電リスト'!$J$5:$J$752,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A20,'架電リスト'!$J$5:$J$807,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A20,'架電リスト'!$J$5:$J$752,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A20,'架電リスト'!$J$5:$J$807,"担当者不在")</f>
         <v/>
       </c>
       <c r="G20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A20,'架電リスト'!$J$5:$J$752,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A20,'架電リスト'!$J$5:$J$807,"資料送付")</f>
         <v/>
       </c>
       <c r="H20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A20,'架電リスト'!$J$5:$J$752,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A20,'架電リスト'!$J$5:$J$807,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A20,'架電リスト'!$J$5:$J$752,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A20,'架電リスト'!$J$5:$J$807,"検討中")</f>
         <v/>
       </c>
       <c r="J20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A20,'架電リスト'!$J$5:$J$752,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A20,'架電リスト'!$J$5:$J$807,"NG")</f>
         <v/>
       </c>
       <c r="K20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A20,'架電リスト'!$J$5:$J$752,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A20,'架電リスト'!$J$5:$J$807,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -46429,43 +49729,43 @@
         </is>
       </c>
       <c r="B21" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$752,A21)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$807,A21)</f>
         <v/>
       </c>
       <c r="C21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,A21,'架電リスト'!$E$5:$E$752,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,A21,'架電リスト'!$E$5:$E$807,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D21" s="16">
-        <f>B21-COUNTIFS('架電リスト'!$B$5:$B$752,A21,'架電リスト'!$J$5:$J$752,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$752,A21,'架電リスト'!$J$5:$J$752,"")</f>
+        <f>B21-COUNTIFS('架電リスト'!$B$5:$B$807,A21,'架電リスト'!$J$5:$J$807,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$807,A21,'架電リスト'!$J$5:$J$807,"")</f>
         <v/>
       </c>
       <c r="E21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A21,'架電リスト'!$J$5:$J$752,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A21,'架電リスト'!$J$5:$J$807,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A21,'架電リスト'!$J$5:$J$752,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A21,'架電リスト'!$J$5:$J$807,"担当者不在")</f>
         <v/>
       </c>
       <c r="G21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A21,'架電リスト'!$J$5:$J$752,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A21,'架電リスト'!$J$5:$J$807,"資料送付")</f>
         <v/>
       </c>
       <c r="H21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A21,'架電リスト'!$J$5:$J$752,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A21,'架電リスト'!$J$5:$J$807,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A21,'架電リスト'!$J$5:$J$752,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A21,'架電リスト'!$J$5:$J$807,"検討中")</f>
         <v/>
       </c>
       <c r="J21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A21,'架電リスト'!$J$5:$J$752,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A21,'架電リスト'!$J$5:$J$807,"NG")</f>
         <v/>
       </c>
       <c r="K21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A21,'架電リスト'!$J$5:$J$752,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A21,'架電リスト'!$J$5:$J$807,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -46476,43 +49776,43 @@
         </is>
       </c>
       <c r="B22" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$752,A22)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$807,A22)</f>
         <v/>
       </c>
       <c r="C22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,A22,'架電リスト'!$E$5:$E$752,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,A22,'架電リスト'!$E$5:$E$807,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D22" s="16">
-        <f>B22-COUNTIFS('架電リスト'!$B$5:$B$752,A22,'架電リスト'!$J$5:$J$752,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$752,A22,'架電リスト'!$J$5:$J$752,"")</f>
+        <f>B22-COUNTIFS('架電リスト'!$B$5:$B$807,A22,'架電リスト'!$J$5:$J$807,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$807,A22,'架電リスト'!$J$5:$J$807,"")</f>
         <v/>
       </c>
       <c r="E22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A22,'架電リスト'!$J$5:$J$752,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A22,'架電リスト'!$J$5:$J$807,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A22,'架電リスト'!$J$5:$J$752,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A22,'架電リスト'!$J$5:$J$807,"担当者不在")</f>
         <v/>
       </c>
       <c r="G22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A22,'架電リスト'!$J$5:$J$752,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A22,'架電リスト'!$J$5:$J$807,"資料送付")</f>
         <v/>
       </c>
       <c r="H22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A22,'架電リスト'!$J$5:$J$752,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A22,'架電リスト'!$J$5:$J$807,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A22,'架電リスト'!$J$5:$J$752,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A22,'架電リスト'!$J$5:$J$807,"検討中")</f>
         <v/>
       </c>
       <c r="J22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A22,'架電リスト'!$J$5:$J$752,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A22,'架電リスト'!$J$5:$J$807,"NG")</f>
         <v/>
       </c>
       <c r="K22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A22,'架電リスト'!$J$5:$J$752,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A22,'架電リスト'!$J$5:$J$807,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -46523,43 +49823,43 @@
         </is>
       </c>
       <c r="B23" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$752,A23)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$807,A23)</f>
         <v/>
       </c>
       <c r="C23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,A23,'架電リスト'!$E$5:$E$752,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,A23,'架電リスト'!$E$5:$E$807,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D23" s="16">
-        <f>B23-COUNTIFS('架電リスト'!$B$5:$B$752,A23,'架電リスト'!$J$5:$J$752,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$752,A23,'架電リスト'!$J$5:$J$752,"")</f>
+        <f>B23-COUNTIFS('架電リスト'!$B$5:$B$807,A23,'架電リスト'!$J$5:$J$807,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$807,A23,'架電リスト'!$J$5:$J$807,"")</f>
         <v/>
       </c>
       <c r="E23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A23,'架電リスト'!$J$5:$J$752,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A23,'架電リスト'!$J$5:$J$807,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A23,'架電リスト'!$J$5:$J$752,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A23,'架電リスト'!$J$5:$J$807,"担当者不在")</f>
         <v/>
       </c>
       <c r="G23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A23,'架電リスト'!$J$5:$J$752,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A23,'架電リスト'!$J$5:$J$807,"資料送付")</f>
         <v/>
       </c>
       <c r="H23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A23,'架電リスト'!$J$5:$J$752,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A23,'架電リスト'!$J$5:$J$807,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A23,'架電リスト'!$J$5:$J$752,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A23,'架電リスト'!$J$5:$J$807,"検討中")</f>
         <v/>
       </c>
       <c r="J23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A23,'架電リスト'!$J$5:$J$752,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A23,'架電リスト'!$J$5:$J$807,"NG")</f>
         <v/>
       </c>
       <c r="K23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A23,'架電リスト'!$J$5:$J$752,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A23,'架電リスト'!$J$5:$J$807,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -46570,90 +49870,137 @@
         </is>
       </c>
       <c r="B24" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$752,A24)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$807,A24)</f>
         <v/>
       </c>
       <c r="C24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,A24,'架電リスト'!$E$5:$E$752,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,A24,'架電リスト'!$E$5:$E$807,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D24" s="16">
-        <f>B24-COUNTIFS('架電リスト'!$B$5:$B$752,A24,'架電リスト'!$J$5:$J$752,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$752,A24,'架電リスト'!$J$5:$J$752,"")</f>
+        <f>B24-COUNTIFS('架電リスト'!$B$5:$B$807,A24,'架電リスト'!$J$5:$J$807,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$807,A24,'架電リスト'!$J$5:$J$807,"")</f>
         <v/>
       </c>
       <c r="E24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A24,'架電リスト'!$J$5:$J$752,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A24,'架電リスト'!$J$5:$J$807,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A24,'架電リスト'!$J$5:$J$752,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A24,'架電リスト'!$J$5:$J$807,"担当者不在")</f>
         <v/>
       </c>
       <c r="G24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A24,'架電リスト'!$J$5:$J$752,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A24,'架電リスト'!$J$5:$J$807,"資料送付")</f>
         <v/>
       </c>
       <c r="H24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A24,'架電リスト'!$J$5:$J$752,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A24,'架電リスト'!$J$5:$J$807,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A24,'架電リスト'!$J$5:$J$752,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A24,'架電リスト'!$J$5:$J$807,"検討中")</f>
         <v/>
       </c>
       <c r="J24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A24,'架電リスト'!$J$5:$J$752,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A24,'架電リスト'!$J$5:$J$807,"NG")</f>
         <v/>
       </c>
       <c r="K24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$752,$A24,'架電リスト'!$J$5:$J$752,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A24,'架電リスト'!$J$5:$J$807,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="17" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="B25" s="16">
+        <f>COUNTIF('架電リスト'!$B$5:$B$807,A25)</f>
+        <v/>
+      </c>
+      <c r="C25" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,A25,'架電リスト'!$E$5:$E$807,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="D25" s="16">
+        <f>B25-COUNTIFS('架電リスト'!$B$5:$B$807,A25,'架電リスト'!$J$5:$J$807,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$807,A25,'架電リスト'!$J$5:$J$807,"")</f>
+        <v/>
+      </c>
+      <c r="E25" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A25,'架電リスト'!$J$5:$J$807,"不在・折返し待ち")</f>
+        <v/>
+      </c>
+      <c r="F25" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A25,'架電リスト'!$J$5:$J$807,"担当者不在")</f>
+        <v/>
+      </c>
+      <c r="G25" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A25,'架電リスト'!$J$5:$J$807,"資料送付")</f>
+        <v/>
+      </c>
+      <c r="H25" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A25,'架電リスト'!$J$5:$J$807,"アポ獲得")</f>
+        <v/>
+      </c>
+      <c r="I25" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A25,'架電リスト'!$J$5:$J$807,"検討中")</f>
+        <v/>
+      </c>
+      <c r="J25" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A25,'架電リスト'!$J$5:$J$807,"NG")</f>
+        <v/>
+      </c>
+      <c r="K25" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$807,$A25,'架電リスト'!$J$5:$J$807,"番号不明")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B25" s="17">
-        <f>SUM(B4:B24)</f>
+      <c r="B26" s="17">
+        <f>SUM(B4:B25)</f>
         <v/>
       </c>
-      <c r="C25" s="17">
-        <f>SUM(C4:C24)</f>
+      <c r="C26" s="17">
+        <f>SUM(C4:C25)</f>
         <v/>
       </c>
-      <c r="D25" s="17">
-        <f>SUM(D4:D24)</f>
+      <c r="D26" s="17">
+        <f>SUM(D4:D25)</f>
         <v/>
       </c>
-      <c r="E25" s="17">
-        <f>SUM(E4:E24)</f>
+      <c r="E26" s="17">
+        <f>SUM(E4:E25)</f>
         <v/>
       </c>
-      <c r="F25" s="17">
-        <f>SUM(F4:F24)</f>
+      <c r="F26" s="17">
+        <f>SUM(F4:F25)</f>
         <v/>
       </c>
-      <c r="G25" s="17">
-        <f>SUM(G4:G24)</f>
+      <c r="G26" s="17">
+        <f>SUM(G4:G25)</f>
         <v/>
       </c>
-      <c r="H25" s="17">
-        <f>SUM(H4:H24)</f>
+      <c r="H26" s="17">
+        <f>SUM(H4:H25)</f>
         <v/>
       </c>
-      <c r="I25" s="17">
-        <f>SUM(I4:I24)</f>
+      <c r="I26" s="17">
+        <f>SUM(I4:I25)</f>
         <v/>
       </c>
-      <c r="J25" s="17">
-        <f>SUM(J4:J24)</f>
+      <c r="J26" s="17">
+        <f>SUM(J4:J25)</f>
         <v/>
       </c>
-      <c r="K25" s="17">
-        <f>SUM(K4:K24)</f>
+      <c r="K26" s="17">
+        <f>SUM(K4:K25)</f>
         <v/>
       </c>
     </row>
@@ -46743,7 +50090,7 @@
     <row r="11">
       <c r="A11" s="19" t="inlineStr">
         <is>
-          <t>・出典：ご提供いただいた学校ネットの検索結果（私立高校・北海道・東北・関東・中部21都道県、748校）の貼り付けデータ。並び順は都道府県ごとに元データの掲載順です。</t>
+          <t>・出典：ご提供いただいた学校ネットの検索結果（私立高校・北海道・東北・関東・中部22都道県、803校）の貼り付けデータ。並び順は都道府県ごとに元データの掲載順です。</t>
         </is>
       </c>
     </row>
